--- a/tame_output/ON/bt/strategyON_20240423.xlsx
+++ b/tame_output/ON/bt/strategyON_20240423.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>55.8%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.8%</t>
+          <t>116.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.7%</t>
+          <t>136.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.4%</t>
+          <t>-57.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>371.6%</t>
+          <t>375.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-579.0%</t>
+          <t>-579.1%</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.9%</t>
+          <t>-44.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-40.2%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-266.2%</t>
+          <t>-266.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-38.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.5%</t>
+          <t>-167.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-294.4%</t>
+          <t>-291.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-211.3%</t>
+          <t>-209.5%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998562</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757924</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.299918119296837</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.07084256347893</v>
+        <v>-10.99385541164535</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.286784359287209</v>
+        <v>-1.255989498553777</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.080560488661919</v>
+        <v>-3.049747960965442</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.29357279722096</v>
+        <v>1.312060313838846</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.99737273181148</v>
+        <v>-10.9203855799779</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.242024725126808</v>
+        <v>-1.211229864393376</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.00709065699447</v>
+        <v>-2.976278129297994</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.35302639771485</v>
+        <v>1.371513914332736</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.17249714919803</v>
+        <v>-11.09550999736445</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.297519271333909</v>
+        <v>-1.266724410600476</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.182215074381014</v>
+        <v>-3.151402546684538</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.262506968030441</v>
+        <v>1.280994484648327</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.40694924321252</v>
+        <v>-11.32996209137893</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.398519273841301</v>
+        <v>-1.367724413107868</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.182215074381014</v>
+        <v>-3.151402546684538</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.255287803128845</v>
+        <v>1.273775319746731</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.69475308774975</v>
+        <v>-11.61776593591617</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.520313002430173</v>
+        <v>-1.48951814169674</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.470018918918252</v>
+        <v>-3.439206391221776</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.075933305632526</v>
+        <v>1.094420822250411</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.92457753491358</v>
+        <v>-11.84759038308</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.611126991457146</v>
+        <v>-1.580332130723714</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.632666455988413</v>
+        <v>-3.601853928291936</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9794605732289856</v>
+        <v>0.9979480898468713</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.15660645464984</v>
+        <v>-12.07961930281626</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.701244830722537</v>
+        <v>-1.670449969989104</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.694679153176836</v>
+        <v>-3.66386662548036</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9449466835450462</v>
+        <v>0.9634342001629324</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.10459094068103</v>
+        <v>-12.02760378884745</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.676448289448611</v>
+        <v>-1.645653428715178</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.694679153176836</v>
+        <v>-3.66386662548036</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.948937019231447</v>
+        <v>0.9674245358493332</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.24626278240515</v>
+        <v>-12.16927563057157</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.734592253037</v>
+        <v>-1.703797392303568</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.694679153176836</v>
+        <v>-3.66386662548036</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9474617923327053</v>
+        <v>0.9659493089505915</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.34516952286442</v>
+        <v>-12.26818237103084</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.759101539055838</v>
+        <v>-1.728306678322406</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.793585893636112</v>
+        <v>-3.762773365939635</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9031711582220123</v>
+        <v>0.9216586748398985</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.14601741562733</v>
+        <v>-12.06903026379374</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.692491829807681</v>
+        <v>-1.661696969074249</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.628263367686298</v>
+        <v>-3.597450839989822</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9893135401452176</v>
+        <v>1.007801056763103</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.92017226290791</v>
+        <v>-11.84318511107433</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.592574695683708</v>
+        <v>-1.561779834950276</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.586336692099135</v>
+        <v>-3.555524164402658</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.024048618533724</v>
+        <v>1.04253613515161</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.63389745058522</v>
+        <v>-11.55691029875164</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.476925626198572</v>
+        <v>-1.446130765465139</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.586336692099135</v>
+        <v>-3.555524164402658</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.025187763089783</v>
+        <v>1.043675279707669</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.68679273862951</v>
+        <v>-11.60980558679593</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.495449967254179</v>
+        <v>-1.464655106520746</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.581381346010688</v>
+        <v>-3.550568818314212</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.030794744904958</v>
+        <v>1.049282261522845</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.40288400770076</v>
+        <v>-11.32589685586718</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.376152770644043</v>
+        <v>-1.34535790991061</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.581381346010688</v>
+        <v>-3.550568818314212</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.036528449143595</v>
+        <v>1.055015965761481</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.28746308356266</v>
+        <v>-11.21047593172908</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.33972166338267</v>
+        <v>-1.308926802649237</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.465960421872593</v>
+        <v>-3.435147894176116</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.096043741232587</v>
+        <v>1.114531257850473</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.02362621635859</v>
+        <v>-10.94663906452501</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.244070397813949</v>
+        <v>-1.213275537080517</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.465960421872593</v>
+        <v>-3.435147894176116</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.08616025991968</v>
+        <v>1.104647776537566</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.75638441549019</v>
+        <v>-10.67939726365661</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.139008237965963</v>
+        <v>-1.108213377232531</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.465960421872593</v>
+        <v>-3.435147894176116</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.084325699420306</v>
+        <v>1.102813216038192</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.63307848701197</v>
+        <v>-10.55609133517839</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.089986181548137</v>
+        <v>-1.059191320814704</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.37654275074503</v>
+        <v>-3.345730223048553</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.137675987123383</v>
+        <v>1.156163503741269</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.60912494603602</v>
+        <v>-10.53213779420244</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.079736259012261</v>
+        <v>-1.048941398278827</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.352589209769072</v>
+        <v>-3.321776682072596</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.152716617854451</v>
+        <v>1.171204134472337</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.34506500771322</v>
+        <v>-10.26807785587964</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9873725998448935</v>
+        <v>-0.9565777391114612</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.088529271446276</v>
+        <v>-3.057716743749799</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.297892264686377</v>
+        <v>1.316379781304263</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.637985384208383</v>
+        <v>-9.560998232374802</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7073277841032595</v>
+        <v>-0.6765329233698272</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.088529271446276</v>
+        <v>-3.057716743749799</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.295105231026076</v>
+        <v>1.313592747643962</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.597801085842192</v>
+        <v>-9.520813934008611</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6909104408689419</v>
+        <v>-0.6601155801355096</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.048344973080085</v>
+        <v>-3.017532445383608</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.319559433933632</v>
+        <v>1.338046950551518</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609647</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.517731290304388</v>
+        <v>-9.440744138470807</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6595157014330635</v>
+        <v>-0.6287208406996307</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.968275177542281</v>
+        <v>-2.937462649845804</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.366968132477071</v>
+        <v>1.385455649094957</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.28425006807479</v>
+        <v>-9.207262916241209</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5581987837033719</v>
+        <v>-0.5274039229699392</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.734793955312683</v>
+        <v>-2.703981427616206</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.514981294652682</v>
+        <v>1.533468811270569</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.104541537930917</v>
+        <v>-9.027554386097336</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4892075819587816</v>
+        <v>-0.4584127212253493</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.677622451149987</v>
+        <v>-2.64680992345351</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.546391986837341</v>
+        <v>1.564879503455227</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860424</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.97226606430003</v>
+        <v>-8.895278912466448</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4409299057593996</v>
+        <v>-0.4101350450259673</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.5453469775191</v>
+        <v>-2.514534449822623</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.6211247577629</v>
+        <v>1.639612274380786</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.781666389626876</v>
+        <v>-8.704679237793295</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3618749752025017</v>
+        <v>-0.3310801144690689</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.354747302845948</v>
+        <v>-2.323934775149471</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.738299623254428</v>
+        <v>1.756787139872314</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.532666590943295</v>
+        <v>-8.455679439109714</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2493687145054104</v>
+        <v>-0.2185738537719781</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.354747302845948</v>
+        <v>-2.323934775149471</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.751205964478087</v>
+        <v>1.769693481095973</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.6382565807164</v>
+        <v>-8.561269428882818</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4195806400138711</v>
+        <v>-0.3887857792804383</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.460337292619052</v>
+        <v>-2.429524764922575</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.559876041015005</v>
+        <v>1.578363557632891</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.656991482834997</v>
+        <v>-8.580004331001415</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3785302589842234</v>
+        <v>-0.3477353982507907</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.460337292619052</v>
+        <v>-2.429524764922575</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.608420382892092</v>
+        <v>1.626907899509978</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180806</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.509051441427397</v>
+        <v>-8.432064289593816</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4392331651093513</v>
+        <v>-0.4084383043759185</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.440016376710494</v>
+        <v>-2.409203849014018</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.500734009749059</v>
+        <v>1.519221526366945</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879199</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.382159034992327</v>
+        <v>-8.305171883158746</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3971901887888012</v>
+        <v>-0.3663953280553689</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.313123970275424</v>
+        <v>-2.282311442578948</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.568155467356622</v>
+        <v>1.586642983974509</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568103</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.338610628221636</v>
+        <v>-8.261623476388054</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3867314381756177</v>
+        <v>-0.3559365774421854</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.313123970275424</v>
+        <v>-2.282311442578948</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.561194855261529</v>
+        <v>1.579682371879416</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963414</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.096462234767777</v>
+        <v>-8.019475082934196</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2754097264129314</v>
+        <v>-0.2446148656794991</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.313123970275424</v>
+        <v>-2.282311442578948</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.575657209642672</v>
+        <v>1.594144726260559</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192812</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.03323286299943</v>
+        <v>-7.956245711165848</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2555858572463974</v>
+        <v>-0.2247909965129646</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.313123970275424</v>
+        <v>-2.282311442578948</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.570189330101867</v>
+        <v>1.588676846719754</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.846745170622424</v>
+        <v>-7.769758018788842</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1834926862850184</v>
+        <v>-0.1526978255515856</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.126636277898418</v>
+        <v>-2.095823750201941</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.679580039538648</v>
+        <v>1.698067556156534</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.825595971718981</v>
+        <v>-7.748608819885399</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1673320284863156</v>
+        <v>-0.1365371677528828</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.105487078994975</v>
+        <v>-2.074674551298498</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.699970537118039</v>
+        <v>1.718458053735926</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788088</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.581830529735536</v>
+        <v>-7.504843377901954</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.07404514334588752</v>
+        <v>-0.04325028261245434</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.105487078994975</v>
+        <v>-2.074674551298498</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.69575124546509</v>
+        <v>1.714238762082976</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.317802462542277</v>
+        <v>-7.240815310708694</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.03369039745143265</v>
+        <v>0.06448525818486583</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.903621680179021</v>
+        <v>-1.872809152482544</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.818994798674678</v>
+        <v>1.837482315292564</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749178</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.067952068593202</v>
+        <v>-6.990964916759619</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1263726300147643</v>
+        <v>0.1571674907481975</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.903621680179021</v>
+        <v>-1.872809152482544</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.81173687365838</v>
+        <v>1.830224390276266</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.764384579589223</v>
+        <v>-6.68739742775564</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2513987491370049</v>
+        <v>0.2821936098704381</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.903621680179021</v>
+        <v>-1.872809152482544</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.815335997179029</v>
+        <v>1.833823513796915</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.69090467073721</v>
+        <v>-6.613917518903627</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2941182187323639</v>
+        <v>0.3249130794657971</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.830141771327007</v>
+        <v>-1.79932924363053</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.872751448544791</v>
+        <v>1.891238965162678</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102775</v>
+        <v>3.773761647102779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.465871671068387</v>
+        <v>-6.388884519234804</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3831518962161899</v>
+        <v>0.4139467569496231</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.605108771658184</v>
+        <v>-1.574296243961707</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.006791725962382</v>
+        <v>2.025279242580268</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353067</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.25123729343198</v>
+        <v>-6.174250141598397</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.47370044832507</v>
+        <v>0.5044953090585031</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.390474394021777</v>
+        <v>-1.3596618663253</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.140267153598543</v>
+        <v>2.15875467021643</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544776</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.984636936457628</v>
+        <v>-5.907649784624045</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5615348498986066</v>
+        <v>0.5923297106320398</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.390474394021777</v>
+        <v>-1.3596618663253</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.121461412382339</v>
+        <v>2.139948929000225</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712288</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.744206439652768</v>
+        <v>-5.667219287819185</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6594501252454279</v>
+        <v>0.6902449859788611</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.150043897216917</v>
+        <v>-1.11923136952044</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.267462787090133</v>
+        <v>2.285950303708018</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.821589933837681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.501415632003322</v>
+        <v>-5.424428480169739</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7604957621400263</v>
+        <v>0.7912906228734595</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.150043897216917</v>
+        <v>-1.11923136952044</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.271392100924953</v>
+        <v>2.289879617542839</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.385475782378137</v>
+        <v>-5.308488630544554</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8075502859074404</v>
+        <v>0.8383451466408736</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.073222166200793</v>
+        <v>-1.042409638504316</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.318163723451967</v>
+        <v>2.336651240069853</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.848613050972337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.142820193954973</v>
+        <v>-5.06583304212139</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9016105924966995</v>
+        <v>0.9324054532301327</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.073222166200793</v>
+        <v>-1.042409638504316</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.31516179467196</v>
+        <v>2.333649311289847</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145932</v>
+        <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.922799395917963</v>
+        <v>-4.84581224408438</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9911979487221179</v>
+        <v>1.021992809455551</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9320023211328128</v>
+        <v>-0.901189793436336</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.401472738723363</v>
+        <v>2.419960255341249</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009944</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.723550766013154</v>
+        <v>-4.646563614179571</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.086791583485865</v>
+        <v>1.117586444219298</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9320023211328128</v>
+        <v>-0.901189793436336</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.417366921525186</v>
+        <v>2.435854438143072</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966252</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.564035662493784</v>
+        <v>-4.487048510660201</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.151743469333915</v>
+        <v>1.182538330067348</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7724872176134429</v>
+        <v>-0.7416746899169661</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.51422182807711</v>
+        <v>2.532709344694996</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046989</v>
+        <v>3.791269976046994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.419363517394046</v>
+        <v>-4.342376365560463</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.219700429935249</v>
+        <v>1.250495290668683</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6278150725137055</v>
+        <v>-0.5970025448172287</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.611113217698392</v>
+        <v>2.629600734316278</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412096</v>
+        <v>3.735835647412101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.401594058463091</v>
+        <v>-4.324606906629508</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.142147905594353</v>
+        <v>1.172942766327786</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6100456135827499</v>
+        <v>-0.5792330858862731</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.537114585143687</v>
+        <v>2.555602101761573</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144509</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.314794560684081</v>
+        <v>-4.237807408850498</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.199268198028523</v>
+        <v>1.230063058761956</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6100456135827499</v>
+        <v>-0.5792330858862731</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.559515078466253</v>
+        <v>2.578002595084139</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.729142822900692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.21510194595507</v>
+        <v>-4.138114794121487</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.23921764529354</v>
+        <v>1.270012506026973</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5103529988537381</v>
+        <v>-0.4795404711572613</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.619403048677072</v>
+        <v>2.637890565294958</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473594</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.28347213227908</v>
+        <v>-4.206484980445497</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.222876493238638</v>
+        <v>1.253671353972071</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5010772998175231</v>
+        <v>-0.4702647721210464</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.635975390573503</v>
+        <v>2.65446290719139</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978363</v>
+        <v>3.714175563978368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.162055702652603</v>
+        <v>-4.08506855081902</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.26187977372112</v>
+        <v>1.292674634454553</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5010772998175231</v>
+        <v>-0.4702647721210464</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.626412099205395</v>
+        <v>2.644899615823281</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.193048861981309</v>
+        <v>-4.116061710147726</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.074192075030024</v>
+        <v>1.104986935763458</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5010772998175231</v>
+        <v>-0.4702647721210464</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.451121664245782</v>
+        <v>2.469609180863668</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675894</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.017574602188839</v>
+        <v>-3.940587450355256</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.1489490109388</v>
+        <v>1.179743871672233</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5010772998175231</v>
+        <v>-0.4702647721210464</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.455688896237569</v>
+        <v>2.474176412855456</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502074769544</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.128510854830088</v>
+        <v>-4.051523702996505</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.104585983769098</v>
+        <v>1.135380844502531</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5010772998175231</v>
+        <v>-0.4702647721210464</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.455700370124367</v>
+        <v>2.474187886742253</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581285</v>
+        <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.331537432373321</v>
+        <v>-4.254550280539738</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.02650673797171</v>
+        <v>1.057301598705144</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7041038773607566</v>
+        <v>-0.6732913496642798</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.337015808818332</v>
+        <v>2.355503325436219</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.425306480665621</v>
+        <v>3.838693806057323</v>
       </c>
       <c r="C1942" t="n">
         <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.173887467034963</v>
+        <v>-4.175680661492006</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.099739110539186</v>
+        <v>1.099021832756369</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7041038773607566</v>
+        <v>-0.6732913496642798</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.347188195250465</v>
+        <v>2.365675711868351</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240423.xlsx
+++ b/tame_output/ON/bt/strategyON_20240423.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>16.4%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.4%</t>
+          <t>116.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.3%</t>
+          <t>136.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.1%</t>
+          <t>-57.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>375.0%</t>
+          <t>371.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-579.1%</t>
+          <t>-593.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.7%</t>
+          <t>-44.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-39.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-266.3%</t>
+          <t>-271.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-36.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.6%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.2%</t>
+          <t>-167.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-291.3%</t>
+          <t>-308.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-209.5%</t>
+          <t>-219.9%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511404</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296837</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.99385541164535</v>
+        <v>-11.07084256347893</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.255989498553777</v>
+        <v>-1.286784359287209</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.049747960965442</v>
+        <v>-3.080560488661919</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.312060313838846</v>
+        <v>1.29357279722096</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.9203855799779</v>
+        <v>-10.99737273181148</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.211229864393376</v>
+        <v>-1.242024725126808</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.976278129297994</v>
+        <v>-3.00709065699447</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.371513914332736</v>
+        <v>1.35302639771485</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.09550999736445</v>
+        <v>-11.17249714919803</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.266724410600476</v>
+        <v>-1.297519271333909</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.151402546684538</v>
+        <v>-3.182215074381014</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.280994484648327</v>
+        <v>1.262506968030441</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.32996209137893</v>
+        <v>-11.40694924321252</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.367724413107868</v>
+        <v>-1.398519273841301</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.151402546684538</v>
+        <v>-3.182215074381014</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.273775319746731</v>
+        <v>1.255287803128845</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.61776593591617</v>
+        <v>-11.69475308774975</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.48951814169674</v>
+        <v>-1.520313002430173</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.439206391221776</v>
+        <v>-3.470018918918252</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.094420822250411</v>
+        <v>1.075933305632526</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.84759038308</v>
+        <v>-11.92457753491358</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.580332130723714</v>
+        <v>-1.611126991457146</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.601853928291936</v>
+        <v>-3.632666455988413</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9979480898468713</v>
+        <v>0.9794605732289856</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.07961930281626</v>
+        <v>-12.15660645464984</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.670449969989104</v>
+        <v>-1.701244830722537</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.66386662548036</v>
+        <v>-3.694679153176836</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9634342001629324</v>
+        <v>0.9449466835450462</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.02760378884745</v>
+        <v>-12.10459094068103</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.645653428715178</v>
+        <v>-1.676448289448611</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.66386662548036</v>
+        <v>-3.694679153176836</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9674245358493332</v>
+        <v>0.948937019231447</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.16927563057157</v>
+        <v>-12.24626278240515</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.703797392303568</v>
+        <v>-1.734592253037</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.66386662548036</v>
+        <v>-3.694679153176836</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9659493089505915</v>
+        <v>0.9474617923327053</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.26818237103084</v>
+        <v>-12.34516952286442</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.728306678322406</v>
+        <v>-1.759101539055838</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.762773365939635</v>
+        <v>-3.793585893636112</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9216586748398985</v>
+        <v>0.9031711582220123</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.06903026379374</v>
+        <v>-12.14601741562733</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.661696969074249</v>
+        <v>-1.692491829807681</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.597450839989822</v>
+        <v>-3.628263367686298</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.007801056763103</v>
+        <v>0.9893135401452176</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.84318511107433</v>
+        <v>-11.92017226290791</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.561779834950276</v>
+        <v>-1.592574695683708</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.555524164402658</v>
+        <v>-3.586336692099135</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.04253613515161</v>
+        <v>1.024048618533724</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.55691029875164</v>
+        <v>-11.63389745058522</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.446130765465139</v>
+        <v>-1.476925626198572</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.555524164402658</v>
+        <v>-3.586336692099135</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.043675279707669</v>
+        <v>1.025187763089783</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.60980558679593</v>
+        <v>-11.68679273862951</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.464655106520746</v>
+        <v>-1.495449967254179</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.550568818314212</v>
+        <v>-3.581381346010688</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.049282261522845</v>
+        <v>1.030794744904958</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.32589685586718</v>
+        <v>-11.40288400770076</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.34535790991061</v>
+        <v>-1.376152770644043</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.550568818314212</v>
+        <v>-3.581381346010688</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.055015965761481</v>
+        <v>1.036528449143595</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.21047593172908</v>
+        <v>-11.28746308356266</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.308926802649237</v>
+        <v>-1.33972166338267</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.435147894176116</v>
+        <v>-3.465960421872593</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.114531257850473</v>
+        <v>1.096043741232587</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.94663906452501</v>
+        <v>-11.02362621635859</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.213275537080517</v>
+        <v>-1.244070397813949</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.435147894176116</v>
+        <v>-3.465960421872593</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.104647776537566</v>
+        <v>1.08616025991968</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.67939726365661</v>
+        <v>-10.75638441549019</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.108213377232531</v>
+        <v>-1.139008237965963</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.435147894176116</v>
+        <v>-3.465960421872593</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.102813216038192</v>
+        <v>1.084325699420306</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.55609133517839</v>
+        <v>-10.63307848701197</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.059191320814704</v>
+        <v>-1.089986181548137</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.345730223048553</v>
+        <v>-3.37654275074503</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.156163503741269</v>
+        <v>1.137675987123383</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.53213779420244</v>
+        <v>-10.60912494603602</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.048941398278827</v>
+        <v>-1.079736259012261</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.321776682072596</v>
+        <v>-3.352589209769072</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.171204134472337</v>
+        <v>1.152716617854451</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487771</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.26807785587964</v>
+        <v>-10.34506500771322</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9565777391114612</v>
+        <v>-0.9873725998448935</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.057716743749799</v>
+        <v>-3.088529271446276</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.316379781304263</v>
+        <v>1.297892264686377</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.560998232374802</v>
+        <v>-9.637985384208383</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6765329233698272</v>
+        <v>-0.7073277841032595</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.057716743749799</v>
+        <v>-3.088529271446276</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.313592747643962</v>
+        <v>1.295105231026076</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.520813934008611</v>
+        <v>-9.597801085842192</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6601155801355096</v>
+        <v>-0.6909104408689419</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.017532445383608</v>
+        <v>-3.048344973080085</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.338046950551518</v>
+        <v>1.319559433933632</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.440744138470807</v>
+        <v>-9.517731290304388</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6287208406996307</v>
+        <v>-0.6595157014330635</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.937462649845804</v>
+        <v>-2.968275177542281</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.385455649094957</v>
+        <v>1.366968132477071</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.207262916241209</v>
+        <v>-9.28425006807479</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5274039229699392</v>
+        <v>-0.5581987837033719</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.703981427616206</v>
+        <v>-2.734793955312683</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.533468811270569</v>
+        <v>1.514981294652682</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.027554386097336</v>
+        <v>-9.104541537930917</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4584127212253493</v>
+        <v>-0.4892075819587816</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.64680992345351</v>
+        <v>-2.677622451149987</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.564879503455227</v>
+        <v>1.546391986837341</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.895278912466448</v>
+        <v>-8.97226606430003</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4101350450259673</v>
+        <v>-0.4409299057593996</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.514534449822623</v>
+        <v>-2.5453469775191</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.639612274380786</v>
+        <v>1.6211247577629</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.704679237793295</v>
+        <v>-8.781666389626876</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3310801144690689</v>
+        <v>-0.3618749752025017</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.323934775149471</v>
+        <v>-2.354747302845948</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.756787139872314</v>
+        <v>1.738299623254428</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.455679439109714</v>
+        <v>-8.532666590943295</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2185738537719781</v>
+        <v>-0.2493687145054104</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.323934775149471</v>
+        <v>-2.354747302845948</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.769693481095973</v>
+        <v>1.751205964478087</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.561269428882818</v>
+        <v>-8.6382565807164</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3887857792804383</v>
+        <v>-0.4195806400138711</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.429524764922575</v>
+        <v>-2.460337292619052</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.578363557632891</v>
+        <v>1.559876041015005</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.580004331001415</v>
+        <v>-8.656991482834997</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3477353982507907</v>
+        <v>-0.3785302589842234</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.429524764922575</v>
+        <v>-2.460337292619052</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.626907899509978</v>
+        <v>1.608420382892092</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180806</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.432064289593816</v>
+        <v>-8.509051441427397</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4084383043759185</v>
+        <v>-0.4392331651093513</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.409203849014018</v>
+        <v>-2.440016376710494</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.519221526366945</v>
+        <v>1.500734009749059</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.305171883158746</v>
+        <v>-8.382159034992327</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3663953280553689</v>
+        <v>-0.3971901887888012</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.282311442578948</v>
+        <v>-2.313123970275424</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.586642983974509</v>
+        <v>1.568155467356622</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568103</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.261623476388054</v>
+        <v>-8.338610628221636</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3559365774421854</v>
+        <v>-0.3867314381756177</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.282311442578948</v>
+        <v>-2.313123970275424</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.579682371879416</v>
+        <v>1.561194855261529</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963414</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.019475082934196</v>
+        <v>-8.096462234767777</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2446148656794991</v>
+        <v>-0.2754097264129314</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.282311442578948</v>
+        <v>-2.313123970275424</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.594144726260559</v>
+        <v>1.575657209642672</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.956245711165848</v>
+        <v>-8.03323286299943</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2247909965129646</v>
+        <v>-0.2555858572463974</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.282311442578948</v>
+        <v>-2.313123970275424</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.588676846719754</v>
+        <v>1.570189330101867</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.769758018788842</v>
+        <v>-7.846745170622424</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1526978255515856</v>
+        <v>-0.1834926862850184</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.095823750201941</v>
+        <v>-2.126636277898418</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.698067556156534</v>
+        <v>1.679580039538648</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.748608819885399</v>
+        <v>-7.825595971718981</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1365371677528828</v>
+        <v>-0.1673320284863156</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.074674551298498</v>
+        <v>-2.105487078994975</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.718458053735926</v>
+        <v>1.699970537118039</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.504843377901954</v>
+        <v>-7.581830529735536</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.04325028261245434</v>
+        <v>-0.07404514334588752</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.074674551298498</v>
+        <v>-2.105487078994975</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.714238762082976</v>
+        <v>1.69575124546509</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.240815310708694</v>
+        <v>-7.317802462542277</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.06448525818486583</v>
+        <v>0.03369039745143265</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.872809152482544</v>
+        <v>-1.903621680179021</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.837482315292564</v>
+        <v>1.818994798674678</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.990964916759619</v>
+        <v>-7.067952068593202</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1571674907481975</v>
+        <v>0.1263726300147643</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.872809152482544</v>
+        <v>-1.903621680179021</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.830224390276266</v>
+        <v>1.81173687365838</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.68739742775564</v>
+        <v>-6.764384579589223</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2821936098704381</v>
+        <v>0.2513987491370049</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.872809152482544</v>
+        <v>-1.903621680179021</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.833823513796915</v>
+        <v>1.815335997179029</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.613917518903627</v>
+        <v>-6.69090467073721</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3249130794657971</v>
+        <v>0.2941182187323639</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.79932924363053</v>
+        <v>-1.830141771327007</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.891238965162678</v>
+        <v>1.872751448544791</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102779</v>
+        <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.388884519234804</v>
+        <v>-6.465871671068387</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4139467569496231</v>
+        <v>0.3831518962161899</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.574296243961707</v>
+        <v>-1.605108771658184</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.025279242580268</v>
+        <v>2.006791725962382</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.174250141598397</v>
+        <v>-6.25123729343198</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5044953090585031</v>
+        <v>0.47370044832507</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.3596618663253</v>
+        <v>-1.390474394021777</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.15875467021643</v>
+        <v>2.140267153598543</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.907649784624045</v>
+        <v>-5.984636936457628</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5923297106320398</v>
+        <v>0.5615348498986066</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.3596618663253</v>
+        <v>-1.390474394021777</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.139948929000225</v>
+        <v>2.121461412382339</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.797691308712288</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.667219287819185</v>
+        <v>-5.744206439652768</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6902449859788611</v>
+        <v>0.6594501252454279</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.11923136952044</v>
+        <v>-1.150043897216917</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.285950303708018</v>
+        <v>2.267462787090133</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837681</v>
+        <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.424428480169739</v>
+        <v>-5.501415632003322</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7912906228734595</v>
+        <v>0.7604957621400263</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.11923136952044</v>
+        <v>-1.150043897216917</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.289879617542839</v>
+        <v>2.271392100924953</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.308488630544554</v>
+        <v>-5.385475782378137</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8383451466408736</v>
+        <v>0.8075502859074404</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.042409638504316</v>
+        <v>-1.073222166200793</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.336651240069853</v>
+        <v>2.318163723451967</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972337</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.06583304212139</v>
+        <v>-5.142820193954973</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9324054532301327</v>
+        <v>0.9016105924966995</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.042409638504316</v>
+        <v>-1.073222166200793</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.333649311289847</v>
+        <v>2.31516179467196</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818665376145932</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.84581224408438</v>
+        <v>-4.922799395917963</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.021992809455551</v>
+        <v>0.9911979487221179</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.901189793436336</v>
+        <v>-0.9320023211328128</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.419960255341249</v>
+        <v>2.401472738723363</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.646563614179571</v>
+        <v>-4.723550766013154</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.117586444219298</v>
+        <v>1.086791583485865</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.901189793436336</v>
+        <v>-0.9320023211328128</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.435854438143072</v>
+        <v>2.417366921525186</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966252</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.487048510660201</v>
+        <v>-4.564035662493784</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.182538330067348</v>
+        <v>1.151743469333915</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7416746899169661</v>
+        <v>-0.7724872176134429</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.532709344694996</v>
+        <v>2.51422182807711</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046989</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.342376365560463</v>
+        <v>-4.561830227672191</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.250495290668683</v>
+        <v>1.162713745823992</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5970025448172287</v>
+        <v>-0.77028178279185</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.629600734316278</v>
+        <v>2.525633191531505</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412101</v>
+        <v>3.735835647412096</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.324606906629508</v>
+        <v>-4.544060768741235</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.172942766327786</v>
+        <v>1.085161221483096</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5792330858862731</v>
+        <v>-0.7525123238608944</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.555602101761573</v>
+        <v>2.451634558976801</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144509</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.237807408850498</v>
+        <v>-4.457261270962226</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.230063058761956</v>
+        <v>1.142281513917265</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5792330858862731</v>
+        <v>-0.7525123238608944</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.578002595084139</v>
+        <v>2.474035052299367</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900692</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.138114794121487</v>
+        <v>-4.357568656233214</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.270012506026973</v>
+        <v>1.182230961182282</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4795404711572613</v>
+        <v>-0.6528197091318826</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.637890565294958</v>
+        <v>2.533923022510186</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473594</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.206484980445497</v>
+        <v>-4.425938842557224</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.253671353972071</v>
+        <v>1.16588980912738</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4702647721210464</v>
+        <v>-0.6435440100956676</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.65446290719139</v>
+        <v>2.550495364406617</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978368</v>
+        <v>3.714175563978363</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.08506855081902</v>
+        <v>-4.304522412930748</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.292674634454553</v>
+        <v>1.204893089609862</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4702647721210464</v>
+        <v>-0.6435440100956676</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.644899615823281</v>
+        <v>2.540932073038508</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.116061710147726</v>
+        <v>-4.335515572259453</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.104986935763458</v>
+        <v>1.017205390918767</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4702647721210464</v>
+        <v>-0.6435440100956676</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.469609180863668</v>
+        <v>2.365641638078895</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.940587450355256</v>
+        <v>-4.160041312466983</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.179743871672233</v>
+        <v>1.091962326827542</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4702647721210464</v>
+        <v>-0.6435440100956676</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.474176412855456</v>
+        <v>2.370208870070683</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695445</v>
+        <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.051523702996505</v>
+        <v>-4.270977565108232</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.135380844502531</v>
+        <v>1.04759929965784</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4702647721210464</v>
+        <v>-0.6435440100956676</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.474187886742253</v>
+        <v>2.37022034395748</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581293</v>
+        <v>3.773206721581285</v>
       </c>
       <c r="C1941" t="n">
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.254550280539738</v>
+        <v>-4.474004142651466</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.057301598705144</v>
+        <v>0.9695200538604527</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6732913496642798</v>
+        <v>-0.846570587638901</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.355503325436219</v>
+        <v>2.251535782651446</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.838693806057323</v>
+        <v>3.445181680597922</v>
       </c>
       <c r="C1942" t="n">
         <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.175680661492006</v>
+        <v>-4.316078543716173</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.099021832756369</v>
+        <v>1.042862679866702</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6732913496642798</v>
+        <v>-0.846570587638901</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.365675711868351</v>
+        <v>2.261708169083578</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240423.xlsx
+++ b/tame_output/ON/bt/strategyON_20240423.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>51.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-41.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.6%</t>
+          <t>116.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>371.5%</t>
+          <t>374.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-593.2%</t>
+          <t>-578.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-39.5%</t>
+          <t>-50.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-271.9%</t>
+          <t>-273.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.4%</t>
+          <t>-34.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.7%</t>
+          <t>-167.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-308.6%</t>
+          <t>-294.4%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-219.9%</t>
+          <t>-218.1%</t>
         </is>
       </c>
     </row>
@@ -45363,19 +45363,19 @@
         <v>3.763178672860424</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.14833294427436</v>
+        <v>3.080813489259044</v>
       </c>
       <c r="D1905" t="n">
         <v>-8.97226606430003</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4409299057593996</v>
+        <v>-0.5084493607747151</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.5453469775191</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.6211247577629</v>
+        <v>1.553605302747584</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>3.083628549946681</v>
       </c>
       <c r="D1906" t="n">
         <v>-8.781666389626876</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3618749752025017</v>
+        <v>-0.4293944302178172</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.354747302845948</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.738299623254428</v>
+        <v>1.670780168239112</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>3.096534891170339</v>
       </c>
       <c r="D1907" t="n">
         <v>-8.532666590943295</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2493687145054104</v>
+        <v>-0.316888169520726</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.354747302845948</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.751205964478087</v>
+        <v>1.683686509462771</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.036078416586436</v>
+        <v>2.96855896157112</v>
       </c>
       <c r="D1908" t="n">
         <v>-8.6382565807164</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4195806400138711</v>
+        <v>-0.4871000950291871</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.460337292619052</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.559876041015005</v>
+        <v>1.492356585999689</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.084622758463523</v>
+        <v>3.017103303448207</v>
       </c>
       <c r="D1909" t="n">
         <v>-8.656991482834997</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3785302589842234</v>
+        <v>-0.4460497139995394</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.460337292619052</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.608420382892092</v>
+        <v>1.540900927876776</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760330111180806</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.964743835775355</v>
+        <v>2.897224380760039</v>
       </c>
       <c r="D1910" t="n">
         <v>-8.509051441427397</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4392331651093513</v>
+        <v>-0.5067526201246673</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.440016376710494</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.500734009749059</v>
+        <v>1.433214554733743</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.956029849521877</v>
+        <v>2.888510394506561</v>
       </c>
       <c r="D1911" t="n">
         <v>-8.382159034992327</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3971901887888012</v>
+        <v>-0.4647096438041172</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.313123970275424</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.568155467356622</v>
+        <v>1.500636012341307</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568103</v>
+        <v>3.729966140568104</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.949069237426784</v>
+        <v>2.881549782411468</v>
       </c>
       <c r="D1912" t="n">
         <v>-8.338610628221636</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3867314381756177</v>
+        <v>-0.4542508931909337</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.313123970275424</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.561194855261529</v>
+        <v>1.493675400246213</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963414</v>
+        <v>3.782918957963415</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.963531591807927</v>
+        <v>2.896012136792611</v>
       </c>
       <c r="D1913" t="n">
         <v>-8.096462234767777</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2754097264129314</v>
+        <v>-0.3429291814282474</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.313123970275424</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.575657209642672</v>
+        <v>1.508137754627356</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192812</v>
+        <v>3.828547911192813</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.958063712267122</v>
+        <v>2.890544257251806</v>
       </c>
       <c r="D1914" t="n">
         <v>-8.03323286299943</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2555858572463974</v>
+        <v>-0.3231053122617134</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.313123970275424</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.570189330101867</v>
+        <v>1.502669875086551</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.955561806277699</v>
+        <v>2.888042351262383</v>
       </c>
       <c r="D1915" t="n">
         <v>-7.846745170622424</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1834926862850184</v>
+        <v>-0.2510121413003343</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.126636277898418</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.679580039538648</v>
+        <v>1.612060584523332</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.963262784515024</v>
+        <v>2.895743329499708</v>
       </c>
       <c r="D1916" t="n">
         <v>-7.825595971718981</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1673320284863156</v>
+        <v>-0.2348514835016315</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.105487078994975</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.699970537118039</v>
+        <v>1.632451082102723</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788088</v>
+        <v>3.74832483278809</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.959043492862075</v>
+        <v>2.891524037846759</v>
       </c>
       <c r="D1917" t="n">
         <v>-7.581830529735536</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.07404514334588752</v>
+        <v>-0.1415645983612035</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.105487078994975</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.69575124546509</v>
+        <v>1.628231790449774</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527522</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.961167806782091</v>
+        <v>2.893648351766775</v>
       </c>
       <c r="D1918" t="n">
         <v>-7.317802462542277</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.03369039745143265</v>
+        <v>-0.03382905756388332</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.903621680179021</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.818994798674678</v>
+        <v>1.751475343659362</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749178</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.953909881765793</v>
+        <v>2.886390426750477</v>
       </c>
       <c r="D1919" t="n">
         <v>-7.067952068593202</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1263726300147643</v>
+        <v>0.05885317499944831</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.903621680179021</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.81173687365838</v>
+        <v>1.744217418643064</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.957509005286441</v>
+        <v>2.889989550271125</v>
       </c>
       <c r="D1920" t="n">
         <v>-6.764384579589223</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2513987491370049</v>
+        <v>0.1838792941216889</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.903621680179021</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.815335997179029</v>
+        <v>1.747816542163713</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.970836511340995</v>
+        <v>2.903317056325679</v>
       </c>
       <c r="D1921" t="n">
         <v>-6.69090467073721</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2941182187323639</v>
+        <v>0.2265987637170479</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.830141771327007</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.872751448544791</v>
+        <v>1.805231993529475</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102775</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.969856988957292</v>
+        <v>2.902337533941976</v>
       </c>
       <c r="D1922" t="n">
         <v>-6.465871671068387</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3831518962161899</v>
+        <v>0.315632441200874</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.605108771658184</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.006791725962382</v>
+        <v>1.939272270947066</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353067</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.974551790011609</v>
+        <v>2.907032334996293</v>
       </c>
       <c r="D1923" t="n">
         <v>-6.25123729343198</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.47370044832507</v>
+        <v>0.406180993309754</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.390474394021777</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.140267153598543</v>
+        <v>2.072747698583227</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544776</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.955746048795405</v>
+        <v>2.888226593780089</v>
       </c>
       <c r="D1924" t="n">
         <v>-5.984636936457628</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5615348498986066</v>
+        <v>0.4940153948832906</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.390474394021777</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.121461412382339</v>
+        <v>2.053941957367023</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712288</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.957489125420282</v>
+        <v>2.889969670404966</v>
       </c>
       <c r="D1925" t="n">
         <v>-5.744206439652768</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6594501252454279</v>
+        <v>0.5919306702301119</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.150043897216917</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.267462787090133</v>
+        <v>2.199943332074817</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.961418439255103</v>
+        <v>2.893898984239787</v>
       </c>
       <c r="D1926" t="n">
         <v>-5.501415632003322</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7604957621400263</v>
+        <v>0.6929763071247104</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.150043897216917</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.271392100924953</v>
+        <v>2.203872645909637</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.962097023172443</v>
+        <v>2.894577568157127</v>
       </c>
       <c r="D1927" t="n">
         <v>-5.385475782378137</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8075502859074404</v>
+        <v>0.7400308308921244</v>
       </c>
       <c r="F1927" t="n">
         <v>-1.073222166200793</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.318163723451967</v>
+        <v>2.250644268436651</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.959095094392436</v>
+        <v>2.89157563937712</v>
       </c>
       <c r="D1928" t="n">
         <v>-5.142820193954973</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9016105924966995</v>
+        <v>0.8340911374813835</v>
       </c>
       <c r="F1928" t="n">
         <v>-1.073222166200793</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.31516179467196</v>
+        <v>2.247642339656645</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145932</v>
+        <v>3.818665376145934</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.96067413140305</v>
+        <v>2.893154676387734</v>
       </c>
       <c r="D1929" t="n">
         <v>-4.922799395917963</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9911979487221179</v>
+        <v>0.9236784937068019</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.9320023211328128</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.401472738723363</v>
+        <v>2.333953283708047</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009944</v>
+        <v>3.843270952009946</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.976568314204874</v>
+        <v>2.909048859189558</v>
       </c>
       <c r="D1930" t="n">
         <v>-4.723550766013154</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.086791583485865</v>
+        <v>1.019272128470549</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.9320023211328128</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.417366921525186</v>
+        <v>2.34984746650987</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966252</v>
+        <v>3.845043810966254</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.977714158645175</v>
+        <v>2.910194703629859</v>
       </c>
       <c r="D1931" t="n">
         <v>-4.564035662493784</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.151743469333915</v>
+        <v>1.084224014318599</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.7724872176134429</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.51422182807711</v>
+        <v>2.446702373061794</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046989</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.987802261206615</v>
+        <v>2.920282806191299</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.561830227672191</v>
+        <v>-4.419363517394046</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.162713745823992</v>
+        <v>1.152180974919933</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.77028178279185</v>
+        <v>-0.6278150725137055</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.525633191531505</v>
+        <v>2.543593762683076</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412096</v>
+        <v>3.735835647412098</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.903141953293337</v>
+        <v>2.835622498278021</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.544060768741235</v>
+        <v>-4.401594058463091</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.085161221483096</v>
+        <v>1.074628450579037</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.7525123238608944</v>
+        <v>-0.6100456135827499</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.451634558976801</v>
+        <v>2.469595130128371</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144509</v>
+        <v>3.762643902144511</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.925542446615903</v>
+        <v>2.858022991600587</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.457261270962226</v>
+        <v>-4.314794560684081</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.142281513917265</v>
+        <v>1.131748743013207</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.7525123238608944</v>
+        <v>-0.6100456135827499</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.474035052299367</v>
+        <v>2.491995623450937</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.729142822900689</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.925614847989315</v>
+        <v>2.858095392973999</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.357568656233214</v>
+        <v>-4.21510194595507</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.182230961182282</v>
+        <v>1.171698190278224</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6528197091318826</v>
+        <v>-0.5103529988537381</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.533923022510186</v>
+        <v>2.551883593661756</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473594</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.936621770464017</v>
+        <v>2.869102315448701</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.425938842557224</v>
+        <v>-4.28347213227908</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.16588980912738</v>
+        <v>1.155357038223322</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.6435440100956676</v>
+        <v>-0.5010772998175231</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.550495364406617</v>
+        <v>2.568455935558188</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978363</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.927058479095908</v>
+        <v>2.859539024080592</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.304522412930748</v>
+        <v>-4.162055702652603</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.204893089609862</v>
+        <v>1.194360318705804</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.6435440100956676</v>
+        <v>-0.5010772998175231</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.540932073038508</v>
+        <v>2.558892644190079</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887698</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.751768044136295</v>
+        <v>2.684248589120979</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.335515572259453</v>
+        <v>-4.193048861981309</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.017205390918767</v>
+        <v>1.006672620014708</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.6435440100956676</v>
+        <v>-0.5010772998175231</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.365641638078895</v>
+        <v>2.383602209230466</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675894</v>
+        <v>3.746038950675896</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.756335276128083</v>
+        <v>2.688815821112767</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.160041312466983</v>
+        <v>-4.017574602188839</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.091962326827542</v>
+        <v>1.081429555923484</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.6435440100956676</v>
+        <v>-0.5010772998175231</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.370208870070683</v>
+        <v>2.388169441222253</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502074769544</v>
+        <v>3.765020747695441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.756346750014881</v>
+        <v>2.688827294999565</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.270977565108232</v>
+        <v>-4.128510854830088</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.04759929965784</v>
+        <v>1.037066528753782</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.6435440100956676</v>
+        <v>-0.5010772998175231</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.37022034395748</v>
+        <v>2.388180915109051</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581285</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.759478135234786</v>
+        <v>2.69195868021947</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.474004142651466</v>
+        <v>-4.331537432373321</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9695200538604527</v>
+        <v>0.9589872829563943</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.846570587638901</v>
+        <v>-0.7041038773607566</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.251535782651446</v>
+        <v>2.269496353803016</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.445181680597922</v>
+        <v>3.794088565148503</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.769650521666918</v>
+        <v>2.702131066651603</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.316078543716173</v>
+        <v>-4.173611833438028</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.042862679866702</v>
+        <v>1.032329908962644</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.846570587638901</v>
+        <v>-0.7041038773607566</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.261708169083578</v>
+        <v>2.279668740235149</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240423.xlsx
+++ b/tame_output/ON/bt/strategyON_20240423.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-41.4%</t>
+          <t>-33.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.8%</t>
+          <t>116.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.7%</t>
+          <t>136.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.4%</t>
+          <t>-57.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>374.9%</t>
+          <t>374.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-578.9%</t>
+          <t>-584.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.9%</t>
+          <t>-44.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.2%</t>
+          <t>-43.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-273.0%</t>
+          <t>-275.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-344.3%</t>
+          <t>-315.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-36.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.4%</t>
+          <t>-157.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-294.4%</t>
+          <t>-276.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-207.0%</t>
+          <t>-189.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-218.1%</t>
+          <t>-169.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1942"/>
+  <dimension ref="A1:G1943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705546</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045694</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43739,10 +43739,10 @@
         <v>3.400076924143565</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.672991798008729</v>
+        <v>1.960129031807373</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.143713021080847</v>
+        <v>4.315995361360034</v>
       </c>
     </row>
     <row r="1835">
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831155</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43762,10 +43762,10 @@
         <v>3.398114040069184</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.673833561494035</v>
+        <v>1.96097079529268</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.142475915034376</v>
+        <v>4.314758255313563</v>
       </c>
     </row>
     <row r="1836">
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.31188830135569</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43785,10 +43785,10 @@
         <v>3.335664557519712</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.659272487791352</v>
+        <v>1.946409721589996</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.113564543440213</v>
+        <v>4.285846883719399</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279815</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43808,10 +43808,10 @@
         <v>3.263351070916398</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.659272487791352</v>
+        <v>1.946409721589996</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.114053682166087</v>
+        <v>4.286336022445274</v>
       </c>
     </row>
     <row r="1838">
@@ -43831,10 +43831,10 @@
         <v>3.248142146799232</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.611050220944268</v>
+        <v>1.898187454742913</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.089200304679504</v>
+        <v>4.26148264495869</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43854,10 +43854,10 @@
         <v>3.188230634556855</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.611050220944268</v>
+        <v>1.898187454742913</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.124141389177046</v>
+        <v>4.296423729456232</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998562</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43877,10 +43877,10 @@
         <v>3.188823111033228</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.666694677210586</v>
+        <v>1.95383191100923</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.156105503122173</v>
+        <v>4.328387843401361</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43900,10 +43900,10 @@
         <v>3.102519060671109</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.504068597245947</v>
+        <v>1.791205831044591</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.037276236767128</v>
+        <v>4.209558577046314</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757924</v>
+        <v>3.293490533757925</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43923,10 +43923,10 @@
         <v>3.077229713781815</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.504068597245947</v>
+        <v>1.791205831044591</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.038293845897598</v>
+        <v>4.210576186176785</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.293766719760743</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43946,10 +43946,10 @@
         <v>3.062443552258887</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.504068597245947</v>
+        <v>1.791205831044591</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.028921877885353</v>
+        <v>4.20120421816454</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706673</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43969,10 +43969,10 @@
         <v>3.019817518043024</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.531104170652084</v>
+        <v>1.818241404450728</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.035225947884274</v>
+        <v>4.207508288163461</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -43992,10 +43992,10 @@
         <v>2.997699191727976</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.531104170652084</v>
+        <v>1.818241404450728</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.039991264717976</v>
+        <v>4.212273604997163</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44015,10 +44015,10 @@
         <v>2.912497674090571</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.323538386260472</v>
+        <v>1.610675620059116</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.913276590202249</v>
+        <v>4.085558930481437</v>
       </c>
     </row>
     <row r="1847">
@@ -44038,10 +44038,10 @@
         <v>2.743322956176899</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9057843627136347</v>
+        <v>1.192921596512279</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.660551067579211</v>
+        <v>3.832833407858397</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44061,10 +44061,10 @@
         <v>2.654540399352574</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8682582290262657</v>
+        <v>1.15539546282491</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.637901603965711</v>
+        <v>3.810183944244898</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44084,10 +44084,10 @@
         <v>2.576230920565269</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8682582290262657</v>
+        <v>1.15539546282491</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.642793748519636</v>
+        <v>3.815076088798823</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44107,10 +44107,10 @@
         <v>2.486747408548067</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6568458081382906</v>
+        <v>0.9439830419369351</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.511027752324839</v>
+        <v>3.683310092604026</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44130,10 +44130,10 @@
         <v>2.344168356819107</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3176874305497686</v>
+        <v>0.604824664348413</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.300617025078175</v>
+        <v>3.472899365357362</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44153,10 +44153,10 @@
         <v>2.233299757866884</v>
       </c>
       <c r="F1852" t="n">
-        <v>-0.0103297911777106</v>
+        <v>0.2768074426209338</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.124144981780456</v>
+        <v>3.296427322059643</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44176,10 +44176,10 @@
         <v>2.044068559661381</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.1153159054173293</v>
+        <v>0.1718213283813151</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.069252063645253</v>
+        <v>3.24153440392444</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44199,10 +44199,10 @@
         <v>1.848220940495474</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.6077009334414261</v>
+        <v>-0.3205636996427816</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.774927438874527</v>
+        <v>2.947209779153714</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44222,10 +44222,10 @@
         <v>1.692691322936309</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.6077009334414261</v>
+        <v>-0.3205636996427816</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.773469977687391</v>
+        <v>2.945752317966577</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44245,10 +44245,10 @@
         <v>1.55698733710026</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.7156069854686442</v>
+        <v>-0.4284697516699998</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.710495469925676</v>
+        <v>2.882777810204862</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44268,10 +44268,10 @@
         <v>1.410033255661178</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.073257335706992</v>
+        <v>-0.7861201019083479</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.492011318438925</v>
+        <v>2.664293658718111</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44291,10 +44291,10 @@
         <v>1.288112541163017</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.073257335706992</v>
+        <v>-0.7861201019083479</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.493784245139184</v>
+        <v>2.666066585418371</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44314,10 +44314,10 @@
         <v>1.101723111370507</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.209674832148259</v>
+        <v>-0.9225375983496149</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.398266634741828</v>
+        <v>2.570548975021015</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44337,10 +44337,10 @@
         <v>0.9961302887195767</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.203338564919004</v>
+        <v>-0.9162013311203597</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.390353170081473</v>
+        <v>2.562635510360659</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44360,10 +44360,10 @@
         <v>0.8604458214833608</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.203338564919004</v>
+        <v>-0.9162013311203597</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.388933761737437</v>
+        <v>2.561216102016624</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44383,10 +44383,10 @@
         <v>0.7214828837574769</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.30156020178613</v>
+        <v>-1.014422967987485</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.336488339851404</v>
+        <v>2.50877068013059</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44406,10 +44406,10 @@
         <v>0.5746864457078096</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.597870986085142</v>
+        <v>-1.310733752286498</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.157956384277828</v>
+        <v>2.330238724557014</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44429,10 +44429,10 @@
         <v>0.4100124788502977</v>
       </c>
       <c r="F1864" t="n">
-        <v>-2.006459763265821</v>
+        <v>-1.719322529467176</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.91156466198418</v>
+        <v>2.083847002263366</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44452,10 +44452,10 @@
         <v>0.2400049176653205</v>
       </c>
       <c r="F1865" t="n">
-        <v>-2.006459763265821</v>
+        <v>-1.719322529467176</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.90675009445564</v>
+        <v>2.079032434734827</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44475,10 +44475,10 @@
         <v>0.07144221855939925</v>
       </c>
       <c r="F1866" t="n">
-        <v>-2.006459763265821</v>
+        <v>-1.719322529467176</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.904744145064518</v>
+        <v>2.077026485343704</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44498,10 +44498,10 @@
         <v>-0.06896989498385953</v>
       </c>
       <c r="F1867" t="n">
-        <v>-2.006459763265821</v>
+        <v>-1.719322529467176</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.915002835733197</v>
+        <v>2.087285176012383</v>
       </c>
     </row>
     <row r="1868">
@@ -44521,10 +44521,10 @@
         <v>-0.2112202586320877</v>
       </c>
       <c r="F1868" t="n">
-        <v>-2.006459763265821</v>
+        <v>-1.719322529467176</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.911102400878891</v>
+        <v>2.083384741158079</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44544,10 +44544,10 @@
         <v>-0.2776722467623243</v>
       </c>
       <c r="F1869" t="n">
-        <v>-2.006459763265821</v>
+        <v>-1.719322529467176</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.909507320933893</v>
+        <v>2.08178966121308</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44567,10 +44567,10 @@
         <v>-0.3925578075571954</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.075202898999699</v>
+        <v>-1.788065665201055</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.872040415422774</v>
+        <v>2.04432275570196</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44590,10 +44590,10 @@
         <v>-0.5699237553356924</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.075202898999699</v>
+        <v>-1.788065665201055</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.868014110888371</v>
+        <v>2.040296451167557</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44613,10 +44613,10 @@
         <v>-0.7232264121543288</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.075202898999699</v>
+        <v>-1.788065665201055</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.867912009566787</v>
+        <v>2.040194349845973</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44636,10 +44636,10 @@
         <v>-0.7836144482681471</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.23260177921282</v>
+        <v>-1.945464545414176</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.776044197410344</v>
+        <v>1.94832653768953</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44659,10 +44659,10 @@
         <v>-0.9220762739716974</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.23260177921282</v>
+        <v>-1.945464545414176</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.781394500708394</v>
+        <v>1.953676840987581</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44682,10 +44682,10 @@
         <v>-1.044720265480525</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.559001807877833</v>
+        <v>-2.271864574079189</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.593470503466564</v>
+        <v>1.765752843745751</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44705,10 +44705,10 @@
         <v>-1.129338102088436</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.778150775952031</v>
+        <v>-2.491013542153386</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.465022873243814</v>
+        <v>1.637305213523001</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44728,10 +44728,10 @@
         <v>-1.127861732105871</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.778150775952031</v>
+        <v>-2.491013542153386</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.465022873243814</v>
+        <v>1.637305213523001</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44751,10 +44751,10 @@
         <v>-1.204051805119175</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.90578972056602</v>
+        <v>-2.618652486767375</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.393952703594063</v>
+        <v>1.56623504387325</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.07084256347893</v>
+        <v>-10.99385541164535</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.286784359287209</v>
+        <v>-1.255989498553777</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.080560488661919</v>
+        <v>-2.762610727166798</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.29357279722096</v>
+        <v>1.484342654118032</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.99737273181148</v>
+        <v>-10.9203855799779</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.242024725126808</v>
+        <v>-1.211229864393376</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.00709065699447</v>
+        <v>-2.689140895499349</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.35302639771485</v>
+        <v>1.543796254611923</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.17249714919803</v>
+        <v>-11.09550999736445</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.297519271333909</v>
+        <v>-1.266724410600476</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.182215074381014</v>
+        <v>-2.864265312885893</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.262506968030441</v>
+        <v>1.453276824927513</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.40694924321252</v>
+        <v>-11.32996209137893</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.398519273841301</v>
+        <v>-1.367724413107868</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.182215074381014</v>
+        <v>-2.864265312885893</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.255287803128845</v>
+        <v>1.446057660025917</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.69475308774975</v>
+        <v>-11.61776593591617</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.520313002430173</v>
+        <v>-1.48951814169674</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.470018918918252</v>
+        <v>-3.152069157423131</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.075933305632526</v>
+        <v>1.266703162529598</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.92457753491358</v>
+        <v>-11.84759038308</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.611126991457146</v>
+        <v>-1.580332130723714</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.632666455988413</v>
+        <v>-3.314716694493292</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9794605732289856</v>
+        <v>1.170230430126058</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.15660645464984</v>
+        <v>-12.07961930281626</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.701244830722537</v>
+        <v>-1.670449969989104</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.694679153176836</v>
+        <v>-3.376729391681715</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9449466835450462</v>
+        <v>1.135716540442119</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.10459094068103</v>
+        <v>-12.02760378884745</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.676448289448611</v>
+        <v>-1.645653428715178</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.694679153176836</v>
+        <v>-3.376729391681715</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.948937019231447</v>
+        <v>1.13970687612852</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.24626278240515</v>
+        <v>-12.16927563057157</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.734592253037</v>
+        <v>-1.703797392303568</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.694679153176836</v>
+        <v>-3.376729391681715</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9474617923327053</v>
+        <v>1.138231649229778</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.34516952286442</v>
+        <v>-12.26818237103084</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.759101539055838</v>
+        <v>-1.728306678322406</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.793585893636112</v>
+        <v>-3.475636132140991</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9031711582220123</v>
+        <v>1.093941015119085</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.14601741562733</v>
+        <v>-12.06903026379374</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.692491829807681</v>
+        <v>-1.661696969074249</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.628263367686298</v>
+        <v>-3.310313606191178</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9893135401452176</v>
+        <v>1.18008339704229</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.92017226290791</v>
+        <v>-11.84318511107433</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.592574695683708</v>
+        <v>-1.561779834950276</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.586336692099135</v>
+        <v>-3.268386930604014</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.024048618533724</v>
+        <v>1.214818475430797</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.63389745058522</v>
+        <v>-11.55691029875164</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.476925626198572</v>
+        <v>-1.446130765465139</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.586336692099135</v>
+        <v>-3.268386930604014</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.025187763089783</v>
+        <v>1.215957619986856</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.68679273862951</v>
+        <v>-11.60980558679593</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.495449967254179</v>
+        <v>-1.464655106520746</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.581381346010688</v>
+        <v>-3.263431584515568</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.030794744904958</v>
+        <v>1.221564601802031</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.40288400770076</v>
+        <v>-11.32589685586718</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.376152770644043</v>
+        <v>-1.34535790991061</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.581381346010688</v>
+        <v>-3.263431584515568</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.036528449143595</v>
+        <v>1.227298306040667</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.28746308356266</v>
+        <v>-11.21047593172908</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.33972166338267</v>
+        <v>-1.308926802649237</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.465960421872593</v>
+        <v>-3.148010660377472</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.096043741232587</v>
+        <v>1.28681359812966</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.02362621635859</v>
+        <v>-10.94663906452501</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.244070397813949</v>
+        <v>-1.213275537080517</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.465960421872593</v>
+        <v>-3.148010660377472</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.08616025991968</v>
+        <v>1.276930116816752</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.75638441549019</v>
+        <v>-10.67939726365661</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.139008237965963</v>
+        <v>-1.108213377232531</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.465960421872593</v>
+        <v>-3.148010660377472</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.084325699420306</v>
+        <v>1.275095556317378</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.63307848701197</v>
+        <v>-10.55609133517839</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.089986181548137</v>
+        <v>-1.059191320814704</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.37654275074503</v>
+        <v>-3.058592989249909</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.137675987123383</v>
+        <v>1.328445844020455</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.60912494603602</v>
+        <v>-10.53213779420244</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.079736259012261</v>
+        <v>-1.048941398278827</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.352589209769072</v>
+        <v>-3.034639448273952</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.152716617854451</v>
+        <v>1.343486474751523</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.34506500771322</v>
+        <v>-10.26807785587964</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9873725998448935</v>
+        <v>-0.9565777391114612</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.088529271446276</v>
+        <v>-2.770579509951155</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.297892264686377</v>
+        <v>1.488662121583449</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.637985384208383</v>
+        <v>-9.560998232374802</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7073277841032595</v>
+        <v>-0.6765329233698272</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.088529271446276</v>
+        <v>-2.770579509951155</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.295105231026076</v>
+        <v>1.485875087923148</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.597801085842192</v>
+        <v>-9.520813934008611</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6909104408689419</v>
+        <v>-0.6601155801355096</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.048344973080085</v>
+        <v>-2.730395211584964</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.319559433933632</v>
+        <v>1.510329290830704</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.517731290304388</v>
+        <v>-9.440744138470807</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6595157014330635</v>
+        <v>-0.6287208406996307</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.968275177542281</v>
+        <v>-2.65032541604716</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.366968132477071</v>
+        <v>1.557737989374143</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.28425006807479</v>
+        <v>-9.207262916241209</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5581987837033719</v>
+        <v>-0.5274039229699392</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.734793955312683</v>
+        <v>-2.416844193817562</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.514981294652682</v>
+        <v>1.705751151549755</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.104541537930917</v>
+        <v>-9.027554386097336</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4892075819587816</v>
+        <v>-0.4584127212253493</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.677622451149987</v>
+        <v>-2.359672689654866</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.546391986837341</v>
+        <v>1.737161843734413</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763178672860424</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.080813489259044</v>
+        <v>3.081729113537891</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.97226606430003</v>
+        <v>-8.895278912466448</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5084493607747151</v>
+        <v>-0.476738875762436</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.5453469775191</v>
+        <v>-2.227397216023979</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.553605302747584</v>
+        <v>1.745290783923503</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.083628549946681</v>
+        <v>3.084544174225528</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.781666389626876</v>
+        <v>-8.704679237793295</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4293944302178172</v>
+        <v>-0.3976839452055376</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.354747302845948</v>
+        <v>-2.036797541350827</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.670780168239112</v>
+        <v>1.862465649415032</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.096534891170339</v>
+        <v>3.097450515449186</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.532666590943295</v>
+        <v>-8.455679439109714</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.316888169520726</v>
+        <v>-0.2851776845084468</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.354747302845948</v>
+        <v>-2.036797541350827</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.683686509462771</v>
+        <v>1.875371990638691</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.96855896157112</v>
+        <v>2.969474585849968</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.6382565807164</v>
+        <v>-8.561269428882818</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4871000950291871</v>
+        <v>-0.455389610016907</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.460337292619052</v>
+        <v>-2.142387531123931</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.492356585999689</v>
+        <v>1.684042067175609</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.017103303448207</v>
+        <v>3.018018927727054</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.656991482834997</v>
+        <v>-8.580004331001415</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4460497139995394</v>
+        <v>-0.4143392289872594</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.460337292619052</v>
+        <v>-2.142387531123931</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.540900927876776</v>
+        <v>1.732586409052695</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760330111180806</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.897224380760039</v>
+        <v>2.898140005038886</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.509051441427397</v>
+        <v>-8.432064289593816</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5067526201246673</v>
+        <v>-0.4750421351123872</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.440016376710494</v>
+        <v>-2.122066615215374</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.433214554733743</v>
+        <v>1.624900035909663</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.888510394506561</v>
+        <v>2.889426018785408</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.382159034992327</v>
+        <v>-8.305171883158746</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4647096438041172</v>
+        <v>-0.4329991587918376</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.313123970275424</v>
+        <v>-1.995174208780304</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.500636012341307</v>
+        <v>1.692321493517226</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568104</v>
+        <v>3.729966140568103</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.881549782411468</v>
+        <v>2.882465406690315</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.338610628221636</v>
+        <v>-8.261623476388054</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4542508931909337</v>
+        <v>-0.4225404081786541</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.313123970275424</v>
+        <v>-1.995174208780304</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.493675400246213</v>
+        <v>1.685360881422133</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963415</v>
+        <v>3.782918957963414</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.896012136792611</v>
+        <v>2.896927761071458</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.096462234767777</v>
+        <v>-8.019475082934196</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3429291814282474</v>
+        <v>-0.3112186964159678</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.313123970275424</v>
+        <v>-1.995174208780304</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.508137754627356</v>
+        <v>1.699823235803276</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192813</v>
+        <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.890544257251806</v>
+        <v>2.891459881530653</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.03323286299943</v>
+        <v>-7.956245711165848</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3231053122617134</v>
+        <v>-0.2913948272494333</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.313123970275424</v>
+        <v>-1.995174208780304</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.502669875086551</v>
+        <v>1.694355356262471</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.888042351262383</v>
+        <v>2.88895797554123</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.846745170622424</v>
+        <v>-7.769758018788842</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2510121413003343</v>
+        <v>-0.2193016562880543</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.126636277898418</v>
+        <v>-1.808686516403297</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.612060584523332</v>
+        <v>1.803746065699252</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.895743329499708</v>
+        <v>2.896658953778555</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.825595971718981</v>
+        <v>-7.748608819885399</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2348514835016315</v>
+        <v>-0.2031409984893515</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.105487078994975</v>
+        <v>-1.787537317499854</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.632451082102723</v>
+        <v>1.824136563278643</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832483278809</v>
+        <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.891524037846759</v>
+        <v>2.892439662125606</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.581830529735536</v>
+        <v>-7.504843377901954</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1415645983612035</v>
+        <v>-0.109854113348923</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.105487078994975</v>
+        <v>-1.787537317499854</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.628231790449774</v>
+        <v>1.819917271625694</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527522</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.893648351766775</v>
+        <v>2.894563976045622</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.317802462542277</v>
+        <v>-7.240815310708694</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.03382905756388332</v>
+        <v>-0.00211857255160286</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.903621680179021</v>
+        <v>-1.585671918683901</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.751475343659362</v>
+        <v>1.943160824835282</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.886390426750477</v>
+        <v>2.887306051029324</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.067952068593202</v>
+        <v>-6.990964916759619</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.05885317499944831</v>
+        <v>0.09056366001172877</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.903621680179021</v>
+        <v>-1.585671918683901</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.744217418643064</v>
+        <v>1.935902899818984</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.889989550271125</v>
+        <v>2.890905174549973</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.764384579589223</v>
+        <v>-6.68739742775564</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1838792941216889</v>
+        <v>0.2155897791339694</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.903621680179021</v>
+        <v>-1.585671918683901</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.747816542163713</v>
+        <v>1.939502023339633</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.903317056325679</v>
+        <v>2.904232680604526</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.69090467073721</v>
+        <v>-6.613917518903627</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2265987637170479</v>
+        <v>0.2583092487293284</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.830141771327007</v>
+        <v>-1.512192009831886</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.805231993529475</v>
+        <v>1.996917474705395</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.902337533941976</v>
+        <v>2.903253158220823</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.465871671068387</v>
+        <v>-6.388884519234804</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.315632441200874</v>
+        <v>0.3473429262131544</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.605108771658184</v>
+        <v>-1.287159010163063</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.939272270947066</v>
+        <v>2.130957752122986</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.907032334996293</v>
+        <v>2.907947959275141</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.25123729343198</v>
+        <v>-6.174250141598397</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.406180993309754</v>
+        <v>0.4378914783220345</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.390474394021777</v>
+        <v>-1.072524632526656</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.072747698583227</v>
+        <v>2.264433179759147</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.888226593780089</v>
+        <v>2.889142218058936</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.984636936457628</v>
+        <v>-5.907649784624045</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4940153948832906</v>
+        <v>0.5257258798955711</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.390474394021777</v>
+        <v>-1.072524632526656</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.053941957367023</v>
+        <v>2.245627438542943</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712288</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.889969670404966</v>
+        <v>2.890885294683814</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.744206439652768</v>
+        <v>-5.667219287819185</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5919306702301119</v>
+        <v>0.6236411552423924</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.150043897216917</v>
+        <v>-0.8320941357217961</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.199943332074817</v>
+        <v>2.391628813250736</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.893898984239787</v>
+        <v>2.894814608518634</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.501415632003322</v>
+        <v>-5.424428480169739</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6929763071247104</v>
+        <v>0.7246867921369908</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.150043897216917</v>
+        <v>-0.8320941357217961</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.203872645909637</v>
+        <v>2.395558127085557</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.894577568157127</v>
+        <v>2.895493192435974</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.385475782378137</v>
+        <v>-5.308488630544554</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7400308308921244</v>
+        <v>0.7717413159044049</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.073222166200793</v>
+        <v>-0.7552724047056723</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.250644268436651</v>
+        <v>2.442329749612571</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.89157563937712</v>
+        <v>2.892491263655967</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.142820193954973</v>
+        <v>-5.06583304212139</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8340911374813835</v>
+        <v>0.865801622493664</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.073222166200793</v>
+        <v>-0.7552724047056723</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.247642339656645</v>
+        <v>2.439327820832564</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145934</v>
+        <v>3.818665376145932</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.893154676387734</v>
+        <v>2.894070300666582</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.922799395917963</v>
+        <v>-4.84581224408438</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9236784937068019</v>
+        <v>0.9553889787190823</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9320023211328128</v>
+        <v>-0.614052559637692</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.333953283708047</v>
+        <v>2.525638764883967</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009946</v>
+        <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.909048859189558</v>
+        <v>2.909964483468405</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.723550766013154</v>
+        <v>-4.646563614179571</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.019272128470549</v>
+        <v>1.050982613482829</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9320023211328128</v>
+        <v>-0.614052559637692</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.34984746650987</v>
+        <v>2.54153294768579</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966254</v>
+        <v>3.845043810966253</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.910194703629859</v>
+        <v>2.911110327908707</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.564035662493784</v>
+        <v>-4.487048510660201</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.084224014318599</v>
+        <v>1.115934499330879</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7724872176134429</v>
+        <v>-0.4545374561183221</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.446702373061794</v>
+        <v>2.638387854237714</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046989</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.920282806191299</v>
+        <v>2.921198430470147</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.419363517394046</v>
+        <v>-4.478495928493547</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.152180974919933</v>
+        <v>1.12944363475898</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6278150725137055</v>
+        <v>-0.4459848739516685</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.543593762683076</v>
+        <v>2.653607506099146</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412098</v>
+        <v>3.735835647412096</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.835622498278021</v>
+        <v>2.836538122556868</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.401594058463091</v>
+        <v>-4.460726469562592</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.074628450579037</v>
+        <v>1.051891110418084</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6100456135827499</v>
+        <v>-0.428215415020713</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.469595130128371</v>
+        <v>2.579608873544441</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144511</v>
+        <v>3.762643902144509</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.858022991600587</v>
+        <v>2.858938615879434</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.314794560684081</v>
+        <v>-4.373926971783582</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.131748743013207</v>
+        <v>1.109011402852254</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6100456135827499</v>
+        <v>-0.428215415020713</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.491995623450937</v>
+        <v>2.602009366867007</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900689</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.858095392973999</v>
+        <v>2.859011017252846</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.21510194595507</v>
+        <v>-4.274234357054571</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.171698190278224</v>
+        <v>1.148960850117271</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5103529988537381</v>
+        <v>-0.3285228002917012</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.551883593661756</v>
+        <v>2.661897337077826</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473594</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.869102315448701</v>
+        <v>2.870017939727548</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.28347213227908</v>
+        <v>-4.342604543378581</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.155357038223322</v>
+        <v>1.132619698062369</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5010772998175231</v>
+        <v>-0.3192471012554863</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.568455935558188</v>
+        <v>2.678469678974257</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978363</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.859539024080592</v>
+        <v>2.86045464835944</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.162055702652603</v>
+        <v>-4.221188113752104</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.194360318705804</v>
+        <v>1.171622978544851</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5010772998175231</v>
+        <v>-0.3192471012554863</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.558892644190079</v>
+        <v>2.668906387606148</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887698</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.684248589120979</v>
+        <v>2.685164213399827</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.193048861981309</v>
+        <v>-4.25218127308081</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.006672620014708</v>
+        <v>0.9839352798537555</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5010772998175231</v>
+        <v>-0.3192471012554863</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.383602209230466</v>
+        <v>2.493615952646535</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675896</v>
+        <v>3.746038950675894</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.688815821112767</v>
+        <v>2.689731445391614</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.017574602188839</v>
+        <v>-4.07670701328834</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.081429555923484</v>
+        <v>1.058692215762531</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5010772998175231</v>
+        <v>-0.3192471012554863</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.388169441222253</v>
+        <v>2.498183184638323</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695441</v>
+        <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.688827294999565</v>
+        <v>2.689742919278412</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.128510854830088</v>
+        <v>-4.187643265929589</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.037066528753782</v>
+        <v>1.014329188592829</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5010772998175231</v>
+        <v>-0.3192471012554863</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.388180915109051</v>
+        <v>2.49819465852512</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581285</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.69195868021947</v>
+        <v>2.692874304498317</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.331537432373321</v>
+        <v>-4.390669843472822</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9589872829563943</v>
+        <v>0.9362499427954414</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7041038773607566</v>
+        <v>-0.5222736787987197</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.269496353803016</v>
+        <v>2.379510097219086</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,45 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.794088565148503</v>
+        <v>3.784340376734155</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.702131066651603</v>
+        <v>2.70304669093045</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.173611833438028</v>
+        <v>-4.232744244537529</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.032329908962644</v>
+        <v>1.009592568801691</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7041038773607566</v>
+        <v>-0.5222736787987197</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.279668740235149</v>
+        <v>2.389682483651218</v>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" s="2" t="n">
+        <v>45405</v>
+      </c>
+      <c r="B1943" t="n">
+        <v>3.793981227243549</v>
+      </c>
+      <c r="C1943" t="n">
+        <v>2.777493156582489</v>
+      </c>
+      <c r="D1943" t="n">
+        <v>-4.232744244537529</v>
+      </c>
+      <c r="E1943" t="n">
+        <v>1.009592568801691</v>
+      </c>
+      <c r="F1943" t="n">
+        <v>-0.5222736787987197</v>
+      </c>
+      <c r="G1943" t="n">
+        <v>2.770556953568856</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240423.xlsx
+++ b/tame_output/ON/bt/strategyON_20240423.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-39.4%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-55.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-80.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.4%</t>
+          <t>117.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.3%</t>
+          <t>137.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-690.5%</t>
+          <t>-715.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.1%</t>
+          <t>-58.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>374.8%</t>
+          <t>440.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-584.8%</t>
+          <t>-603.9%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-276.6%</t>
+          <t>-286.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.7%</t>
+          <t>-45.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-43.7%</t>
+          <t>-57.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-275.3%</t>
+          <t>-276.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-315.6%</t>
+          <t>-343.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.8%</t>
+          <t>-38.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.1%</t>
+          <t>-167.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-276.2%</t>
+          <t>-293.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-189.8%</t>
+          <t>-206.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,42 +1471,42 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-169.0%</t>
+          <t>-190.4%</t>
         </is>
       </c>
     </row>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705546</v>
+        <v>3.311607601705545</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045694</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43739,10 +43739,10 @@
         <v>3.400076924143565</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.960129031807373</v>
+        <v>1.672991798008729</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.315995361360034</v>
+        <v>4.143713021080847</v>
       </c>
     </row>
     <row r="1835">
@@ -43750,22 +43750,22 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831155</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.6507367156124425</v>
+        <v>0.4007055084138003</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.398114040069184</v>
+        <v>3.298101557189727</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.96097079529268</v>
+        <v>1.684470908683104</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.314758255313563</v>
+        <v>4.148858323347817</v>
       </c>
     </row>
     <row r="1836">
@@ -43773,22 +43773,22 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.31188830135569</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.5450498276701428</v>
+        <v>0.2950186204715006</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.335664557519712</v>
+        <v>3.235652074640255</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.946409721589996</v>
+        <v>1.66990983498042</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.285846883719399</v>
+        <v>4.119946951753654</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,22 +43796,22 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279815</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.3630432643471742</v>
+        <v>0.113012057148532</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.263351070916398</v>
+        <v>3.163338588036941</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.946409721589996</v>
+        <v>1.66990983498042</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.286336022445274</v>
+        <v>4.120436090479529</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.3148209975000906</v>
+        <v>0.06478979030144849</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.248142146799232</v>
+        <v>3.148129663919775</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.898187454742913</v>
+        <v>1.621687568133337</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.26148264495869</v>
+        <v>4.095582712992945</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.07768950565029553</v>
+        <v>-0.1723417015483466</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.188230634556855</v>
+        <v>3.088218151677399</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.898187454742913</v>
+        <v>1.621687568133337</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.296423729456232</v>
+        <v>4.130523797490486</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.08272709637788206</v>
+        <v>-0.1673041108207601</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.188823111033228</v>
+        <v>3.088810628153771</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.95383191100923</v>
+        <v>1.677332024399654</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.328387843401361</v>
+        <v>4.162487911435615</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.07989898358675651</v>
+        <v>-0.3299301907853986</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.102519060671109</v>
+        <v>3.002506577791653</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.791205831044591</v>
+        <v>1.514705944435015</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.209558577046314</v>
+        <v>4.043658645080569</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.1456663736361686</v>
+        <v>-0.3956975808348107</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.077229713781815</v>
+        <v>2.977217230902358</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.791205831044591</v>
+        <v>1.514705944435015</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.210576186176785</v>
+        <v>4.044676254211039</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.1592018574128782</v>
+        <v>-0.4092330646115203</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.062443552258887</v>
+        <v>2.96243106937943</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.791205831044591</v>
+        <v>1.514705944435015</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.20120421816454</v>
+        <v>4.035304286198794</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.2409737578406299</v>
+        <v>-0.491004965039272</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.019817518043024</v>
+        <v>2.919805035163567</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.818241404450728</v>
+        <v>1.541741517841152</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.207508288163461</v>
+        <v>4.041608356197715</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.3081828657125075</v>
+        <v>-0.5582140729111497</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.997699191727976</v>
+        <v>2.897686708848519</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.818241404450728</v>
+        <v>1.541741517841152</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.212273604997163</v>
+        <v>4.046373673031417</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.5157486501041194</v>
+        <v>-0.7657798573027615</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.912497674090571</v>
+        <v>2.812485191211114</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.610675620059116</v>
+        <v>1.33417573344954</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.085558930481437</v>
+        <v>3.919658998515691</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.9335026736509564</v>
+        <v>-1.183533880849599</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.743322956176899</v>
+        <v>2.643310473297443</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.192921596512279</v>
+        <v>0.9164217099027029</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.832833407858397</v>
+        <v>3.666933475892651</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.155124607209074</v>
+        <v>-1.405155814407716</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.654540399352574</v>
+        <v>2.554527916473118</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.15539546282491</v>
+        <v>0.8788955762153339</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.810183944244898</v>
+        <v>3.644284012279152</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.363128665562151</v>
+        <v>-1.613159872760793</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.576230920565269</v>
+        <v>2.476218437685812</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.15539546282491</v>
+        <v>0.8788955762153339</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.815076088798823</v>
+        <v>3.649176156833077</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.574541086450126</v>
+        <v>-1.824572293648768</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.486747408548067</v>
+        <v>2.38673492566861</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9439830419369351</v>
+        <v>0.6674831553273588</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.683310092604026</v>
+        <v>3.51741016063828</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.913699464038648</v>
+        <v>-2.163730671237291</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.344168356819107</v>
+        <v>2.24415587393965</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.604824664348413</v>
+        <v>0.3283247777388367</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.472899365357362</v>
+        <v>3.306999433391616</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.241716685766128</v>
+        <v>-2.49174789296477</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.233299757866884</v>
+        <v>2.133287274987427</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.2768074426209338</v>
+        <v>0.0003075560113575682</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.296427322059643</v>
+        <v>3.130527390093897</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.735041557301306</v>
+        <v>-2.985072764499948</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.044068559661381</v>
+        <v>1.944056076781924</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1718213283813151</v>
+        <v>-0.1046785582282612</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.24153440392444</v>
+        <v>3.075634471958694</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.227426585325403</v>
+        <v>-3.477457792524045</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.848220940495474</v>
+        <v>1.748208457616018</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3205636996427816</v>
+        <v>-0.5970635862523579</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.947209779153714</v>
+        <v>2.781309847187968</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.612606976255475</v>
+        <v>-3.862638183454117</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.692691322936309</v>
+        <v>1.592678840056852</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3205636996427816</v>
+        <v>-0.5970635862523579</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.945752317966577</v>
+        <v>2.779852386000831</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.956289749482138</v>
+        <v>-4.20632095668078</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.55698733710026</v>
+        <v>1.456974854220803</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4284697516699998</v>
+        <v>-0.704969638279576</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.882777810204862</v>
+        <v>2.716877878239117</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.313940099720486</v>
+        <v>-4.563971306919128</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.410033255661178</v>
+        <v>1.310020772781721</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.7861201019083479</v>
+        <v>-1.062619988517924</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.664293658718111</v>
+        <v>2.498393726752366</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.623174202716537</v>
+        <v>-4.873205409915179</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.288112541163017</v>
+        <v>1.188100058283561</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.7861201019083479</v>
+        <v>-1.062619988517924</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.666066585418371</v>
+        <v>2.500166653452625</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.054979995866324</v>
+        <v>-5.305011203064966</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.101723111370507</v>
+        <v>1.00171062849105</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.9225375983496149</v>
+        <v>-1.199037484959191</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.570548975021015</v>
+        <v>2.40464904305527</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.289673989998876</v>
+        <v>-5.539705197197518</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9961302887195767</v>
+        <v>0.8961178058401198</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.9162013311203597</v>
+        <v>-1.192701217729936</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.562635510360659</v>
+        <v>2.396735578394913</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.625336637229329</v>
+        <v>-5.875367844427971</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8604458214833608</v>
+        <v>0.7604333386039039</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.9162013311203597</v>
+        <v>-1.192701217729936</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.561216102016624</v>
+        <v>2.395316170050878</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.988962882129642</v>
+        <v>-6.238994089328284</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7214828837574769</v>
+        <v>0.6214704008780201</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.014422967987485</v>
+        <v>-1.290922854597062</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.50877068013059</v>
+        <v>2.342870748164844</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.354090264768389</v>
+        <v>-6.604121471967031</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5746864457078096</v>
+        <v>0.4746739628283527</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.310733752286498</v>
+        <v>-1.587233638896074</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.330238724557014</v>
+        <v>2.164338792591268</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.762679041949067</v>
+        <v>-7.012710249147709</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4100124788502977</v>
+        <v>0.3099999959708408</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.719322529467176</v>
+        <v>-1.995822416076753</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.083847002263366</v>
+        <v>1.91794707029762</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.175661526090161</v>
+        <v>-7.425692733288803</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2400049176653205</v>
+        <v>0.1399924347858637</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.719322529467176</v>
+        <v>-1.995822416076753</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.079032434734827</v>
+        <v>1.913132502769081</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.592053400377158</v>
+        <v>-7.8420846075758</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.07144221855939925</v>
+        <v>-0.0285702643200576</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.719322529467176</v>
+        <v>-1.995822416076753</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.077026485343704</v>
+        <v>1.911126553377958</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.968730410907003</v>
+        <v>-8.218761618105644</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.06896989498385953</v>
+        <v>-0.1689823778633164</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.719322529467176</v>
+        <v>-1.995822416076753</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.087285176012383</v>
+        <v>1.921385244046637</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.314605232891811</v>
+        <v>-8.564636440090453</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2112202586320877</v>
+        <v>-0.3112327415115446</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.719322529467176</v>
+        <v>-1.995822416076753</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.083384741158079</v>
+        <v>1.917484809192333</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.476747503354904</v>
+        <v>-8.726778710553546</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2776722467623243</v>
+        <v>-0.3776847296417811</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.719322529467176</v>
+        <v>-1.995822416076753</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.08178966121308</v>
+        <v>1.915889729247334</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.773408845165102</v>
+        <v>-9.023440052363744</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3925578075571954</v>
+        <v>-0.4925702904366522</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.788065665201055</v>
+        <v>-2.064565551810631</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.04432275570196</v>
+        <v>1.878422823736214</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.206757953275337</v>
+        <v>-9.45678916047398</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5699237553356924</v>
+        <v>-0.6699362382151492</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.788065665201055</v>
+        <v>-2.064565551810631</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.040296451167557</v>
+        <v>1.874396519201811</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.589759342017969</v>
+        <v>-9.839790549216611</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7232264121543288</v>
+        <v>-0.8232388950337857</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.788065665201055</v>
+        <v>-2.064565551810631</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.040194349845973</v>
+        <v>1.874294417880227</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.747158222231089</v>
+        <v>-9.997189429429731</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7836144482681471</v>
+        <v>-0.8836269311476039</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.945464545414176</v>
+        <v>-2.221964432023753</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.94832653768953</v>
+        <v>1.782426605723785</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.10668854473509</v>
+        <v>-10.35671975193373</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9220762739716974</v>
+        <v>-1.022088756851154</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.945464545414176</v>
+        <v>-2.221964432023753</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.953676840987581</v>
+        <v>1.787776909021835</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.4330885734001</v>
+        <v>-10.68311978059875</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.044720265480525</v>
+        <v>-1.144732748359982</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.271864574079189</v>
+        <v>-2.548364460688766</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.765752843745751</v>
+        <v>1.599852911780004</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.6522375414743</v>
+        <v>-10.90226874867294</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.129338102088436</v>
+        <v>-1.229350584967893</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.491013542153386</v>
+        <v>-2.767513428762963</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.637305213523001</v>
+        <v>1.471405281557255</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.64854661651789</v>
+        <v>-10.89857782371653</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.127861732105871</v>
+        <v>-1.227874214985328</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.491013542153386</v>
+        <v>-2.767513428762963</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.637305213523001</v>
+        <v>1.471405281557255</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.85280479184775</v>
+        <v>-11.1028359990464</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.204051805119175</v>
+        <v>-1.304064287998631</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.618652486767375</v>
+        <v>-2.895152373376952</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.56623504387325</v>
+        <v>1.400335111907504</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.99385541164535</v>
+        <v>-11.32087377067757</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.255989498553777</v>
+        <v>-1.386796842166666</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.762610727166798</v>
+        <v>-3.069923141472851</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.484342654118032</v>
+        <v>1.299955205534401</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.9203855799779</v>
+        <v>-11.24740393901013</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.211229864393376</v>
+        <v>-1.342037208006265</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.689140895499349</v>
+        <v>-2.996453309805402</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.543796254611923</v>
+        <v>1.359408806028291</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.09550999736445</v>
+        <v>-11.42252835639667</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.266724410600476</v>
+        <v>-1.397531754213366</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.864265312885893</v>
+        <v>-3.171577727191946</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.453276824927513</v>
+        <v>1.268889376343881</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.32996209137893</v>
+        <v>-11.65698045041116</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.367724413107868</v>
+        <v>-1.498531756720757</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.864265312885893</v>
+        <v>-3.171577727191946</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.446057660025917</v>
+        <v>1.261670211442285</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.61776593591617</v>
+        <v>-11.9447842949484</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.48951814169674</v>
+        <v>-1.62032548530963</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.152069157423131</v>
+        <v>-3.459381571729184</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.266703162529598</v>
+        <v>1.082315713945966</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.84759038308</v>
+        <v>-12.17460874211222</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.580332130723714</v>
+        <v>-1.711139474336603</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.314716694493292</v>
+        <v>-3.622029108799345</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.170230430126058</v>
+        <v>0.9858429815424263</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.07961930281626</v>
+        <v>-12.40663766184848</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.670449969989104</v>
+        <v>-1.801257313601993</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.376729391681715</v>
+        <v>-3.684041805987768</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.135716540442119</v>
+        <v>0.9513290918584869</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.02760378884745</v>
+        <v>-12.35462214787967</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.645653428715178</v>
+        <v>-1.776460772328067</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.376729391681715</v>
+        <v>-3.684041805987768</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.13970687612852</v>
+        <v>0.9553194275448877</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.16927563057157</v>
+        <v>-12.49629398960379</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.703797392303568</v>
+        <v>-1.834604735916457</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.376729391681715</v>
+        <v>-3.684041805987768</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.138231649229778</v>
+        <v>0.9538442006461461</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.26818237103084</v>
+        <v>-12.59520073006307</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.728306678322406</v>
+        <v>-1.859114021935295</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.475636132140991</v>
+        <v>-3.782948546447044</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.093941015119085</v>
+        <v>0.9095535665354531</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.06903026379374</v>
+        <v>-12.39604862282597</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.661696969074249</v>
+        <v>-1.792504312687138</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.310313606191178</v>
+        <v>-3.617626020497231</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.18008339704229</v>
+        <v>0.9956959484586578</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.84318511107433</v>
+        <v>-12.17020347010656</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.561779834950276</v>
+        <v>-1.692587178563166</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.268386930604014</v>
+        <v>-3.575699344910067</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.214818475430797</v>
+        <v>1.030431026847165</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.55691029875164</v>
+        <v>-11.88392865778386</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.446130765465139</v>
+        <v>-1.576938109078029</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.268386930604014</v>
+        <v>-3.575699344910067</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.215957619986856</v>
+        <v>1.031570171403224</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.60980558679593</v>
+        <v>-11.93682394582815</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.464655106520746</v>
+        <v>-1.595462450133636</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.263431584515568</v>
+        <v>-3.570743998821621</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.221564601802031</v>
+        <v>1.037177153218399</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.32589685586718</v>
+        <v>-11.6529152148994</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.34535790991061</v>
+        <v>-1.4761652535235</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.263431584515568</v>
+        <v>-3.570743998821621</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.227298306040667</v>
+        <v>1.042910857457036</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.21047593172908</v>
+        <v>-11.5374942907613</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.308926802649237</v>
+        <v>-1.439734146262126</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.148010660377472</v>
+        <v>-3.455323074683525</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.28681359812966</v>
+        <v>1.102426149546028</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.94663906452501</v>
+        <v>-11.27365742355723</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.213275537080517</v>
+        <v>-1.344082880693406</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.148010660377472</v>
+        <v>-3.455323074683525</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.276930116816752</v>
+        <v>1.09254266823312</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.67939726365661</v>
+        <v>-11.00641562268884</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.108213377232531</v>
+        <v>-1.23902072084542</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.148010660377472</v>
+        <v>-3.455323074683525</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.275095556317378</v>
+        <v>1.090708107733747</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.55609133517839</v>
+        <v>-10.88310969421062</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.059191320814704</v>
+        <v>-1.189998664427593</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.058592989249909</v>
+        <v>-3.365905403555962</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.328445844020455</v>
+        <v>1.144058395436824</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.53213779420244</v>
+        <v>-10.85915615323466</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.048941398278827</v>
+        <v>-1.179748741891717</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.034639448273952</v>
+        <v>-3.341951862580005</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.343486474751523</v>
+        <v>1.159099026167892</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.26807785587964</v>
+        <v>-10.59509621491186</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9565777391114612</v>
+        <v>-1.08738508272435</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.770579509951155</v>
+        <v>-3.077891924257208</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.488662121583449</v>
+        <v>1.304274672999817</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.560998232374802</v>
+        <v>-9.888016591407025</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6765329233698272</v>
+        <v>-0.8073402669827163</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.770579509951155</v>
+        <v>-3.077891924257208</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.485875087923148</v>
+        <v>1.301487639339516</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.520813934008611</v>
+        <v>-9.847832293040835</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6601155801355096</v>
+        <v>-0.7909229237483988</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.730395211584964</v>
+        <v>-3.037707625891017</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.510329290830704</v>
+        <v>1.325941842247072</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.440744138470807</v>
+        <v>-9.76776249750303</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6287208406996307</v>
+        <v>-0.7595281843125203</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.65032541604716</v>
+        <v>-2.957637830353213</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.557737989374143</v>
+        <v>1.373350540790512</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.207262916241209</v>
+        <v>-9.534281275273432</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5274039229699392</v>
+        <v>-0.6582112665828288</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.416844193817562</v>
+        <v>-2.724156608123615</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.705751151549755</v>
+        <v>1.521363702966123</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.027554386097336</v>
+        <v>-9.354572745129559</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4584127212253493</v>
+        <v>-0.5892200648382384</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.359672689654866</v>
+        <v>-2.666985103960919</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.737161843734413</v>
+        <v>1.552774395150782</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763178672860424</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.081729113537891</v>
+        <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.895278912466448</v>
+        <v>-9.222297271498672</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.476738875762436</v>
+        <v>-0.5409423886388565</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.227397216023979</v>
+        <v>-2.534709630330032</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.745290783923503</v>
+        <v>1.62750716607634</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.084544174225528</v>
+        <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.704679237793295</v>
+        <v>-9.031697596825518</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3976839452055376</v>
+        <v>-0.4618874580819585</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.036797541350827</v>
+        <v>-2.34410995565688</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.862465649415032</v>
+        <v>1.744682031567869</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.097450515449186</v>
+        <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.455679439109714</v>
+        <v>-8.782697798141937</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2851776845084468</v>
+        <v>-0.3493811973848673</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.036797541350827</v>
+        <v>-2.34410995565688</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.875371990638691</v>
+        <v>1.757588372791527</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.969474585849968</v>
+        <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.561269428882818</v>
+        <v>-8.888287787915042</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.455389610016907</v>
+        <v>-0.5195931228933279</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.142387531123931</v>
+        <v>-2.449699945429984</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.684042067175609</v>
+        <v>1.566258449328446</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.018018927727054</v>
+        <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.580004331001415</v>
+        <v>-8.907022690033639</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4143392289872594</v>
+        <v>-0.4785427418636803</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.142387531123931</v>
+        <v>-2.449699945429984</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.732586409052695</v>
+        <v>1.614802791205532</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180806</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.898140005038886</v>
+        <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.432064289593816</v>
+        <v>-8.759082648626039</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4750421351123872</v>
+        <v>-0.5392456479888081</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.122066615215374</v>
+        <v>-2.429379029521427</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.624900035909663</v>
+        <v>1.507116418062499</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879199</v>
+        <v>3.7235626538792</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.889426018785408</v>
+        <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.305171883158746</v>
+        <v>-8.632190242190969</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4329991587918376</v>
+        <v>-0.497202671668258</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.995174208780304</v>
+        <v>-2.302486623086357</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.692321493517226</v>
+        <v>1.574537875670063</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568103</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.882465406690315</v>
+        <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.261623476388054</v>
+        <v>-8.588641835420278</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4225404081786541</v>
+        <v>-0.4867439210550746</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.995174208780304</v>
+        <v>-2.302486623086357</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.685360881422133</v>
+        <v>1.56757726357497</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963414</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.896927761071458</v>
+        <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.019475082934196</v>
+        <v>-8.34649344196642</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3112186964159678</v>
+        <v>-0.3754222092923882</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.995174208780304</v>
+        <v>-2.302486623086357</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.699823235803276</v>
+        <v>1.582039617956113</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192812</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.891459881530653</v>
+        <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.956245711165848</v>
+        <v>-8.283264070198072</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2913948272494333</v>
+        <v>-0.3555983401258542</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.995174208780304</v>
+        <v>-2.302486623086357</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.694355356262471</v>
+        <v>1.576571738415308</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.88895797554123</v>
+        <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.769758018788842</v>
+        <v>-8.096776377821065</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2193016562880543</v>
+        <v>-0.2835051691644748</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.808686516403297</v>
+        <v>-2.11599893070935</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.803746065699252</v>
+        <v>1.685962447852089</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.896658953778555</v>
+        <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.748608819885399</v>
+        <v>-8.075627178917621</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2031409984893515</v>
+        <v>-0.267344511365772</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.787537317499854</v>
+        <v>-2.094849731805907</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.824136563278643</v>
+        <v>1.70635294543148</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788088</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.892439662125606</v>
+        <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.504843377901954</v>
+        <v>-7.831861736934177</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.109854113348923</v>
+        <v>-0.1740576262253435</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.787537317499854</v>
+        <v>-2.094849731805907</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.819917271625694</v>
+        <v>1.702133653778531</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.894563976045622</v>
+        <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.240815310708694</v>
+        <v>-7.567833669740917</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.00211857255160286</v>
+        <v>-0.06632208542802376</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.585671918683901</v>
+        <v>-1.892984332989953</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.943160824835282</v>
+        <v>1.825377206988119</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749178</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.887306051029324</v>
+        <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.990964916759619</v>
+        <v>-7.317983275791843</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.09056366001172877</v>
+        <v>0.02636014713530832</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.585671918683901</v>
+        <v>-1.892984332989953</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.935902899818984</v>
+        <v>1.818119281971821</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.890905174549973</v>
+        <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.68739742775564</v>
+        <v>-7.014415786787864</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2155897791339694</v>
+        <v>0.1513862662575485</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.585671918683901</v>
+        <v>-1.892984332989953</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.939502023339633</v>
+        <v>1.82171840549247</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.904232680604526</v>
+        <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.613917518903627</v>
+        <v>-6.94093587793585</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2583092487293284</v>
+        <v>0.1941057358529079</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.512192009831886</v>
+        <v>-1.819504424137939</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.996917474705395</v>
+        <v>1.879133856858232</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102775</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.903253158220823</v>
+        <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.388884519234804</v>
+        <v>-6.715902878267027</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3473429262131544</v>
+        <v>0.283139413336734</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.287159010163063</v>
+        <v>-1.594471424469116</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.130957752122986</v>
+        <v>2.013174134275823</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353067</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.907947959275141</v>
+        <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.174250141598397</v>
+        <v>-6.50126850063062</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4378914783220345</v>
+        <v>0.373687965445614</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.072524632526656</v>
+        <v>-1.379837046832709</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.264433179759147</v>
+        <v>2.146649561911984</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544776</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.889142218058936</v>
+        <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.907649784624045</v>
+        <v>-6.234668143656268</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5257258798955711</v>
+        <v>0.4615223670191502</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.072524632526656</v>
+        <v>-1.379837046832709</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.245627438542943</v>
+        <v>2.12784382069578</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712288</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.890885294683814</v>
+        <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.667219287819185</v>
+        <v>-5.994237646851408</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6236411552423924</v>
+        <v>0.5594376423659719</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8320941357217961</v>
+        <v>-1.139406550027849</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.391628813250736</v>
+        <v>2.273845195403573</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.894814608518634</v>
+        <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.424428480169739</v>
+        <v>-5.751446839201963</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7246867921369908</v>
+        <v>0.6604832792605704</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8320941357217961</v>
+        <v>-1.139406550027849</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.395558127085557</v>
+        <v>2.277774509238394</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.895493192435974</v>
+        <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.308488630544554</v>
+        <v>-5.635506989576777</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7717413159044049</v>
+        <v>0.7075378030279844</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7552724047056723</v>
+        <v>-1.062584819011725</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.442329749612571</v>
+        <v>2.324546131765408</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.892491263655967</v>
+        <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.06583304212139</v>
+        <v>-5.392851401153614</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.865801622493664</v>
+        <v>0.8015981096172435</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7552724047056723</v>
+        <v>-1.062584819011725</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.439327820832564</v>
+        <v>2.321544202985401</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145932</v>
+        <v>3.818665376145934</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.894070300666582</v>
+        <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.84581224408438</v>
+        <v>-5.172830603116603</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9553889787190823</v>
+        <v>0.8911854658426619</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.614052559637692</v>
+        <v>-0.9213649739437451</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.525638764883967</v>
+        <v>2.407855147036804</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009944</v>
+        <v>3.843270952009946</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.909964483468405</v>
+        <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.646563614179571</v>
+        <v>-4.973581973211794</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.050982613482829</v>
+        <v>0.9867791006064086</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.614052559637692</v>
+        <v>-0.9213649739437451</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.54153294768579</v>
+        <v>2.423749329838627</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966253</v>
+        <v>3.845043810966254</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.911110327908707</v>
+        <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.487048510660201</v>
+        <v>-4.814066869692424</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.115934499330879</v>
+        <v>1.051730986454458</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4545374561183221</v>
+        <v>-0.7618498704243751</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.638387854237714</v>
+        <v>2.520604236390551</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046989</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.921198430470147</v>
+        <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.478495928493547</v>
+        <v>-4.669394724592687</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.12944363475898</v>
+        <v>1.119687947055793</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4459848739516685</v>
+        <v>-0.6171777253246378</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.653607506099146</v>
+        <v>2.617495626011833</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412096</v>
+        <v>3.735835647412098</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.836538122556868</v>
+        <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.460726469562592</v>
+        <v>-4.651625265661731</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.051891110418084</v>
+        <v>1.042135422714897</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.428215415020713</v>
+        <v>-0.5994082663936822</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.579608873544441</v>
+        <v>2.543496993457128</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144509</v>
+        <v>3.762643902144511</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.858938615879434</v>
+        <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.373926971783582</v>
+        <v>-4.564825767882722</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.109011402852254</v>
+        <v>1.099255715149067</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.428215415020713</v>
+        <v>-0.5994082663936822</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.602009366867007</v>
+        <v>2.565897486779694</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.729142822900689</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.859011017252846</v>
+        <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.274234357054571</v>
+        <v>-4.46513315315371</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.148960850117271</v>
+        <v>1.139205162414084</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3285228002917012</v>
+        <v>-0.4997156516646704</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.661897337077826</v>
+        <v>2.625785456990513</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473594</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.870017939727548</v>
+        <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.342604543378581</v>
+        <v>-4.53350333947772</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.132619698062369</v>
+        <v>1.122864010359182</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3192471012554863</v>
+        <v>-0.4904399526284555</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.678469678974257</v>
+        <v>2.642357798886944</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978363</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.86045464835944</v>
+        <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.221188113752104</v>
+        <v>-4.412086909851244</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.171622978544851</v>
+        <v>1.161867290841664</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3192471012554863</v>
+        <v>-0.4904399526284555</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.668906387606148</v>
+        <v>2.632794507518835</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.685164213399827</v>
+        <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.25218127308081</v>
+        <v>-4.443080069179949</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9839352798537555</v>
+        <v>0.9741795921505685</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3192471012554863</v>
+        <v>-0.4904399526284555</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.493615952646535</v>
+        <v>2.457504072559222</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675894</v>
+        <v>3.746038950675896</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.689731445391614</v>
+        <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.07670701328834</v>
+        <v>-4.267605809387479</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.058692215762531</v>
+        <v>1.048936528059344</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3192471012554863</v>
+        <v>-0.4904399526284555</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.498183184638323</v>
+        <v>2.46207130455101</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502074769544</v>
+        <v>3.765020747695441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.689742919278412</v>
+        <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.187643265929589</v>
+        <v>-4.378542062028728</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.014329188592829</v>
+        <v>1.004573500889642</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3192471012554863</v>
+        <v>-0.4904399526284555</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.49819465852512</v>
+        <v>2.462082778437808</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581285</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.692874304498317</v>
+        <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.390669843472822</v>
+        <v>-4.581568639571961</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9362499427954414</v>
+        <v>0.9264942550922544</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5222736787987197</v>
+        <v>-0.6934665301716889</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.379510097219086</v>
+        <v>2.343398217131773</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734155</v>
+        <v>3.784340376734157</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.70304669093045</v>
+        <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.232744244537529</v>
+        <v>-4.423643040636668</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.009592568801691</v>
+        <v>0.9998368810985039</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5222736787987197</v>
+        <v>-0.6934665301716889</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.389682483651218</v>
+        <v>2.353570603563905</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.793981227243549</v>
+        <v>3.446164917740473</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.777493156582489</v>
+        <v>2.563211637559666</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.232744244537529</v>
+        <v>-4.423643040636668</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.009592568801691</v>
+        <v>0.9998368810985039</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5222736787987197</v>
+        <v>-0.6934665301716889</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.770556953568856</v>
+        <v>2.556275434546034</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240423.xlsx
+++ b/tame_output/ON/bt/strategyON_20240423.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>51.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-39.4%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-55.3%</t>
+          <t>-34.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.5%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.3%</t>
+          <t>117.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-715.5%</t>
+          <t>-706.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.4%</t>
+          <t>-58.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.7%</t>
+          <t>428.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-603.9%</t>
+          <t>-595.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-286.6%</t>
+          <t>-283.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.7%</t>
+          <t>-45.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-57.3%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.2%</t>
+          <t>-272.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-343.3%</t>
+          <t>-343.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.7%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.0%</t>
+          <t>-167.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-293.3%</t>
+          <t>-293.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-206.4%</t>
+          <t>-206.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-190.4%</t>
+          <t>-169.8%</t>
         </is>
       </c>
     </row>
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.4007055084138003</v>
+        <v>0.6507367156124425</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.298101557189727</v>
+        <v>3.398114040069184</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.684470908683104</v>
+        <v>1.673833561494035</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.148858323347817</v>
+        <v>4.142475915034376</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.2950186204715006</v>
+        <v>0.3818549727391262</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.235652074640255</v>
+        <v>3.270386615547305</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.66990983498042</v>
+        <v>1.664946924712625</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.119946951753654</v>
+        <v>4.116969205592977</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.113012057148532</v>
+        <v>0.1992695863449189</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.163338588036941</v>
+        <v>3.197841599715496</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.66990983498042</v>
+        <v>1.664946924712625</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.120436090479529</v>
+        <v>4.117458344318852</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.06478979030144849</v>
+        <v>0.1510473194978354</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.148129663919775</v>
+        <v>3.18263267559833</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.621687568133337</v>
+        <v>1.616724657865542</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.095582712992945</v>
+        <v>4.092604966832268</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.1723417015483466</v>
+        <v>-0.0860841723519597</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.088218151677399</v>
+        <v>3.122721163355953</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.621687568133337</v>
+        <v>1.616724657865542</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.130523797490486</v>
+        <v>4.127546051329809</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.1673041108207601</v>
+        <v>-0.08104658162437317</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.088810628153771</v>
+        <v>3.123313639832326</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.677332024399654</v>
+        <v>1.672369114131859</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.162487911435615</v>
+        <v>4.159510165274938</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.3299301907853986</v>
+        <v>-0.2436726615890117</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.002506577791653</v>
+        <v>3.037009589470208</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.514705944435015</v>
+        <v>1.50974303416722</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.043658645080569</v>
+        <v>4.040680898919891</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757925</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3956975808348107</v>
+        <v>-0.3094400516384238</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.977217230902358</v>
+        <v>3.011720242580913</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.514705944435015</v>
+        <v>1.50974303416722</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.044676254211039</v>
+        <v>4.041698508050362</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.4092330646115203</v>
+        <v>-0.3229755354151334</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.96243106937943</v>
+        <v>2.996934081057985</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.514705944435015</v>
+        <v>1.50974303416722</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.035304286198794</v>
+        <v>4.032326540038118</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.491004965039272</v>
+        <v>-0.4047474358428851</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.919805035163567</v>
+        <v>2.954308046842122</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.541741517841152</v>
+        <v>1.536778607573357</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.041608356197715</v>
+        <v>4.038630610037038</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5582140729111497</v>
+        <v>-0.4719565437147628</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.897686708848519</v>
+        <v>2.932189720527073</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.541741517841152</v>
+        <v>1.536778607573357</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.046373673031417</v>
+        <v>4.04339592687074</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7657798573027615</v>
+        <v>-0.6795223281063747</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.812485191211114</v>
+        <v>2.846988202889669</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.33417573344954</v>
+        <v>1.329212823181745</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.919658998515691</v>
+        <v>3.916681252355014</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.183533880849599</v>
+        <v>-1.097276351653212</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.643310473297443</v>
+        <v>2.677813484975998</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9164217099027029</v>
+        <v>0.9114587996349081</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.666933475892651</v>
+        <v>3.663955729731974</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.405155814407716</v>
+        <v>-1.318898285211329</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.554527916473118</v>
+        <v>2.589030928151672</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8788955762153339</v>
+        <v>0.873932665947539</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.644284012279152</v>
+        <v>3.641306266118475</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.613159872760793</v>
+        <v>-1.526902343564406</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.476218437685812</v>
+        <v>2.510721449364366</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8788955762153339</v>
+        <v>0.873932665947539</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.649176156833077</v>
+        <v>3.6461984106724</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.824572293648768</v>
+        <v>-1.738314764452381</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.38673492566861</v>
+        <v>2.421237937347165</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6674831553273588</v>
+        <v>0.662520245059564</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.51741016063828</v>
+        <v>3.514432414477603</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.163730671237291</v>
+        <v>-2.077473142040904</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.24415587393965</v>
+        <v>2.278658885618205</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3283247777388367</v>
+        <v>0.3233618674710419</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.306999433391616</v>
+        <v>3.304021687230939</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.49174789296477</v>
+        <v>-2.405490363768383</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.133287274987427</v>
+        <v>2.167790286665982</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.0003075560113575682</v>
+        <v>-0.004655354256437261</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.130527390093897</v>
+        <v>3.12754964393322</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.985072764499948</v>
+        <v>-2.898815235303561</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.944056076781924</v>
+        <v>1.978559088460479</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.1046785582282612</v>
+        <v>-0.109641468496056</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.075634471958694</v>
+        <v>3.072656725798017</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.477457792524045</v>
+        <v>-3.391200263327658</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.748208457616018</v>
+        <v>1.782711469294572</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.5970635862523579</v>
+        <v>-0.6020264965201527</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.781309847187968</v>
+        <v>2.778332101027291</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.862638183454117</v>
+        <v>-3.77638065425773</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.592678840056852</v>
+        <v>1.627181851735406</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.5970635862523579</v>
+        <v>-0.6020264965201527</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.779852386000831</v>
+        <v>2.776874639840154</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.20632095668078</v>
+        <v>-4.120063427484393</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.456974854220803</v>
+        <v>1.491477865899358</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.704969638279576</v>
+        <v>-0.7099325485473709</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.716877878239117</v>
+        <v>2.71390013207844</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.563971306919128</v>
+        <v>-4.477713777722741</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.310020772781721</v>
+        <v>1.344523784460276</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.062619988517924</v>
+        <v>-1.067582898785719</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.498393726752366</v>
+        <v>2.495415980591689</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.873205409915179</v>
+        <v>-4.786947880718792</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.188100058283561</v>
+        <v>1.222603069962116</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.062619988517924</v>
+        <v>-1.067582898785719</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.500166653452625</v>
+        <v>2.497188907291948</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.305011203064966</v>
+        <v>-5.218753673868579</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.00171062849105</v>
+        <v>1.036213640169605</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.199037484959191</v>
+        <v>-1.204000395226986</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.40464904305527</v>
+        <v>2.401671296894593</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.539705197197518</v>
+        <v>-5.453447668001131</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.8961178058401198</v>
+        <v>0.9306208175186748</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.192701217729936</v>
+        <v>-1.197664127997731</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.396735578394913</v>
+        <v>2.393757832234237</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.875367844427971</v>
+        <v>-5.789110315231584</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7604333386039039</v>
+        <v>0.7949363502824589</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.192701217729936</v>
+        <v>-1.197664127997731</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.395316170050878</v>
+        <v>2.392338423890202</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.238994089328284</v>
+        <v>-6.152736560131897</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6214704008780201</v>
+        <v>0.655973412556575</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.290922854597062</v>
+        <v>-1.295885764864857</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.342870748164844</v>
+        <v>2.339893002004167</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.604121471967031</v>
+        <v>-6.517863942770644</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.4746739628283527</v>
+        <v>0.5091769745069077</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.587233638896074</v>
+        <v>-1.592196549163869</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.164338792591268</v>
+        <v>2.161361046430592</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-7.012710249147709</v>
+        <v>-6.926452719951323</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3099999959708408</v>
+        <v>0.3445030076493953</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.995822416076753</v>
+        <v>-2.000785326344547</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.91794707029762</v>
+        <v>1.914969324136943</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.425692733288803</v>
+        <v>-7.339435204092417</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1399924347858637</v>
+        <v>0.1744954464644182</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.995822416076753</v>
+        <v>-2.000785326344547</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.913132502769081</v>
+        <v>1.910154756608404</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.8420846075758</v>
+        <v>-7.755827078379414</v>
       </c>
       <c r="E1866" t="n">
-        <v>-0.0285702643200576</v>
+        <v>0.005932747358496471</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.995822416076753</v>
+        <v>-2.000785326344547</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.911126553377958</v>
+        <v>1.908148807217281</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.218761618105644</v>
+        <v>-8.132504088909258</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1689823778633164</v>
+        <v>-0.1344793661847619</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.995822416076753</v>
+        <v>-2.000785326344547</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.921385244046637</v>
+        <v>1.91840749788596</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.564636440090453</v>
+        <v>-8.478378910894067</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.3112327415115446</v>
+        <v>-0.2767297298329905</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.995822416076753</v>
+        <v>-2.000785326344547</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.917484809192333</v>
+        <v>1.914507063031656</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.726778710553546</v>
+        <v>-8.64052118135716</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3776847296417811</v>
+        <v>-0.3431817179632266</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.995822416076753</v>
+        <v>-2.000785326344547</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.915889729247334</v>
+        <v>1.912911983086657</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-9.023440052363744</v>
+        <v>-8.937182523167358</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4925702904366522</v>
+        <v>-0.4580672787580977</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.064565551810631</v>
+        <v>-2.069528462078426</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.878422823736214</v>
+        <v>1.875445077575538</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.45678916047398</v>
+        <v>-9.370531631277593</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6699362382151492</v>
+        <v>-0.6354332265365947</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.064565551810631</v>
+        <v>-2.069528462078426</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.874396519201811</v>
+        <v>1.871418773041135</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.839790549216611</v>
+        <v>-9.753533020020225</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.8232388950337857</v>
+        <v>-0.7887358833552316</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.064565551810631</v>
+        <v>-2.069528462078426</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.874294417880227</v>
+        <v>1.871316671719551</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.997189429429731</v>
+        <v>-9.910931900233345</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8836269311476039</v>
+        <v>-0.8491239194690494</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.221964432023753</v>
+        <v>-2.226927342291547</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.782426605723785</v>
+        <v>1.779448859563108</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.35671975193373</v>
+        <v>-10.27046222273735</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.022088756851154</v>
+        <v>-0.9875857451726002</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.221964432023753</v>
+        <v>-2.226927342291547</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.787776909021835</v>
+        <v>1.784799162861158</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.68311978059875</v>
+        <v>-10.59686225140236</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.144732748359982</v>
+        <v>-1.110229736681428</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.548364460688766</v>
+        <v>-2.55332737095656</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.599852911780004</v>
+        <v>1.596875165619328</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.90226874867294</v>
+        <v>-10.81601121947656</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.229350584967893</v>
+        <v>-1.194847573289338</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.767513428762963</v>
+        <v>-2.772476339030757</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.471405281557255</v>
+        <v>1.468427535396578</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.89857782371653</v>
+        <v>-10.81232029452015</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.227874214985328</v>
+        <v>-1.193371203306774</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.767513428762963</v>
+        <v>-2.772476339030757</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.471405281557255</v>
+        <v>1.468427535396578</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.1028359990464</v>
+        <v>-11.01657846985001</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.304064287998631</v>
+        <v>-1.269561276320077</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.895152373376952</v>
+        <v>-2.900115283644746</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.400335111907504</v>
+        <v>1.397357365746827</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.32087377067757</v>
+        <v>-11.23461624148119</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.386796842166666</v>
+        <v>-1.352293830488112</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.069923141472851</v>
+        <v>-3.074886051740645</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.299955205534401</v>
+        <v>1.296977459373724</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.24740393901013</v>
+        <v>-11.16114640981374</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.342037208006265</v>
+        <v>-1.307534196327711</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.996453309805402</v>
+        <v>-3.001416220073197</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.359408806028291</v>
+        <v>1.356431059867614</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.42252835639667</v>
+        <v>-11.33627082720028</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.397531754213366</v>
+        <v>-1.363028742534811</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.171577727191946</v>
+        <v>-3.176540637459741</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.268889376343881</v>
+        <v>1.265911630183205</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.65698045041116</v>
+        <v>-11.57072292121477</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.498531756720757</v>
+        <v>-1.464028745042203</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.171577727191946</v>
+        <v>-3.176540637459741</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.261670211442285</v>
+        <v>1.258692465281609</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.9447842949484</v>
+        <v>-11.85852676575201</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.62032548530963</v>
+        <v>-1.585822473631075</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.459381571729184</v>
+        <v>-3.464344481996979</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.082315713945966</v>
+        <v>1.079337967785289</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.17460874211222</v>
+        <v>-12.08835121291584</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.711139474336603</v>
+        <v>-1.676636462658049</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.622029108799345</v>
+        <v>-3.626992019067139</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9858429815424263</v>
+        <v>0.9828652353817495</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.40663766184848</v>
+        <v>-12.3203801326521</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.801257313601993</v>
+        <v>-1.766754301923439</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.684041805987768</v>
+        <v>-3.689004716255563</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9513290918584869</v>
+        <v>0.9483513456978105</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.35462214787967</v>
+        <v>-12.26836461868328</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.776460772328067</v>
+        <v>-1.741957760649512</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.684041805987768</v>
+        <v>-3.689004716255563</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9553194275448877</v>
+        <v>0.9523416813842114</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.49629398960379</v>
+        <v>-12.4100364604074</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.834604735916457</v>
+        <v>-1.800101724237902</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.684041805987768</v>
+        <v>-3.689004716255563</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9538442006461461</v>
+        <v>0.9508664544854697</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.59520073006307</v>
+        <v>-12.50894320086668</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.859114021935295</v>
+        <v>-1.824611010256741</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.782948546447044</v>
+        <v>-3.787911456714838</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9095535665354531</v>
+        <v>0.9065758203747762</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.39604862282597</v>
+        <v>-12.30979109362958</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.792504312687138</v>
+        <v>-1.758001301008584</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.617626020497231</v>
+        <v>-3.622588930765025</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9956959484586578</v>
+        <v>0.9927182022979815</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.17020347010656</v>
+        <v>-12.08394594091017</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.692587178563166</v>
+        <v>-1.65808416688461</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.575699344910067</v>
+        <v>-3.580662255177861</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.030431026847165</v>
+        <v>1.027453280686488</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.88392865778386</v>
+        <v>-11.79767112858747</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.576938109078029</v>
+        <v>-1.542435097399473</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.575699344910067</v>
+        <v>-3.580662255177861</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.031570171403224</v>
+        <v>1.028592425242547</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.93682394582815</v>
+        <v>-11.85056641663176</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.595462450133636</v>
+        <v>-1.560959438455081</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.570743998821621</v>
+        <v>-3.575706909089415</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.037177153218399</v>
+        <v>1.034199407057722</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.6529152148994</v>
+        <v>-11.56665768570301</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.4761652535235</v>
+        <v>-1.441662241844944</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.570743998821621</v>
+        <v>-3.575706909089415</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.042910857457036</v>
+        <v>1.039933111296359</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.5374942907613</v>
+        <v>-11.45123676156492</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.439734146262126</v>
+        <v>-1.405231134583572</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.455323074683525</v>
+        <v>-3.460285984951319</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.102426149546028</v>
+        <v>1.099448403385351</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.27365742355723</v>
+        <v>-11.18739989436085</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.344082880693406</v>
+        <v>-1.309579869014851</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.455323074683525</v>
+        <v>-3.460285984951319</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.09254266823312</v>
+        <v>1.089564922072443</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-11.00641562268884</v>
+        <v>-10.92015809349245</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.23902072084542</v>
+        <v>-1.204517709166865</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.455323074683525</v>
+        <v>-3.460285984951319</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.090708107733747</v>
+        <v>1.08773036157307</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.88310969421062</v>
+        <v>-10.79685216501423</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.189998664427593</v>
+        <v>-1.155495652749039</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.365905403555962</v>
+        <v>-3.370868313823757</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.144058395436824</v>
+        <v>1.141080649276147</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.85915615323466</v>
+        <v>-10.77289862403827</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.179748741891717</v>
+        <v>-1.145245730213162</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.341951862580005</v>
+        <v>-3.346914772847799</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.159099026167892</v>
+        <v>1.156121280007215</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.59509621491186</v>
+        <v>-10.50883868571547</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.08738508272435</v>
+        <v>-1.052882071045795</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.077891924257208</v>
+        <v>-3.082854834525003</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.304274672999817</v>
+        <v>1.301296926839141</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.888016591407025</v>
+        <v>-9.801759062210637</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.8073402669827163</v>
+        <v>-0.7728372553041614</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.077891924257208</v>
+        <v>-3.082854834525003</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.301487639339516</v>
+        <v>1.29850989317884</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.847832293040835</v>
+        <v>-9.761574763844447</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7909229237483988</v>
+        <v>-0.7564199120698438</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.037707625891017</v>
+        <v>-3.042670536158812</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.325941842247072</v>
+        <v>1.322964096086396</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.76776249750303</v>
+        <v>-9.681504968306642</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7595281843125203</v>
+        <v>-0.7250251726339649</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.957637830353213</v>
+        <v>-2.962600740621008</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.373350540790512</v>
+        <v>1.370372794629835</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.534281275273432</v>
+        <v>-9.448023746077045</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6582112665828288</v>
+        <v>-0.6237082549042734</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.724156608123615</v>
+        <v>-2.729119518391409</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.521363702966123</v>
+        <v>1.518385956805447</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.354572745129559</v>
+        <v>-9.268315215933171</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5892200648382384</v>
+        <v>-0.5547170531596834</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.666985103960919</v>
+        <v>-2.671948014228713</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.552774395150782</v>
+        <v>1.549796648990105</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.222297271498672</v>
+        <v>-9.136039742302284</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5409423886388565</v>
+        <v>-0.5064393769603015</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.534709630330032</v>
+        <v>-2.539672540597827</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.62750716607634</v>
+        <v>1.624529419915664</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-9.031697596825518</v>
+        <v>-8.94544006762913</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4618874580819585</v>
+        <v>-0.4273844464034031</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.34410995565688</v>
+        <v>-2.349072865924674</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.744682031567869</v>
+        <v>1.741704285407192</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.782697798141937</v>
+        <v>-8.696440268945549</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3493811973848673</v>
+        <v>-0.3148781857063123</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.34410995565688</v>
+        <v>-2.349072865924674</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.757588372791527</v>
+        <v>1.754610626630851</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.888287787915042</v>
+        <v>-8.802030258718654</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.5195931228933279</v>
+        <v>-0.4850901112147725</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.449699945429984</v>
+        <v>-2.454662855697779</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.566258449328446</v>
+        <v>1.563280703167769</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457899</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.907022690033639</v>
+        <v>-8.820765160837251</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4785427418636803</v>
+        <v>-0.4440397301851249</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.449699945429984</v>
+        <v>-2.454662855697779</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.614802791205532</v>
+        <v>1.611825045044856</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180806</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.759082648626039</v>
+        <v>-8.672825119429652</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5392456479888081</v>
+        <v>-0.5047426363102527</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.429379029521427</v>
+        <v>-2.434341939789221</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.507116418062499</v>
+        <v>1.504138671901823</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.7235626538792</v>
+        <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.632190242190969</v>
+        <v>-8.545932712994581</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.497202671668258</v>
+        <v>-0.4626996599897031</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.302486623086357</v>
+        <v>-2.307449533354151</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.574537875670063</v>
+        <v>1.571560129509386</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568104</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.588641835420278</v>
+        <v>-8.50238430622389</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4867439210550746</v>
+        <v>-0.4522409093765196</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.302486623086357</v>
+        <v>-2.307449533354151</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.56757726357497</v>
+        <v>1.564599517414293</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963415</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.34649344196642</v>
+        <v>-8.260235912770032</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3754222092923882</v>
+        <v>-0.3409191976138333</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.302486623086357</v>
+        <v>-2.307449533354151</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.582039617956113</v>
+        <v>1.579061871795436</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828547911192813</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.283264070198072</v>
+        <v>-8.197006541001684</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3555983401258542</v>
+        <v>-0.3210953284472993</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.302486623086357</v>
+        <v>-2.307449533354151</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.576571738415308</v>
+        <v>1.573593992254631</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.096776377821065</v>
+        <v>-8.010518848624677</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2835051691644748</v>
+        <v>-0.2490021574859198</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.11599893070935</v>
+        <v>-2.120961840977145</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.685962447852089</v>
+        <v>1.682984701691412</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.075627178917621</v>
+        <v>-7.989369649721234</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.267344511365772</v>
+        <v>-0.232841499687217</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.094849731805907</v>
+        <v>-2.099812642073701</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.70635294543148</v>
+        <v>1.703375199270803</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.74832483278809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.831861736934177</v>
+        <v>-7.74560420773779</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1740576262253435</v>
+        <v>-0.1395546145467885</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.094849731805907</v>
+        <v>-2.099812642073701</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.702133653778531</v>
+        <v>1.699155907617854</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.567833669740917</v>
+        <v>-7.481576140544529</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.06632208542802376</v>
+        <v>-0.03181907374946835</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.892984332989953</v>
+        <v>-1.897947243257748</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.825377206988119</v>
+        <v>1.822399460827442</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.317983275791843</v>
+        <v>-7.231725746595455</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.02636014713530832</v>
+        <v>0.06086315881386328</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.892984332989953</v>
+        <v>-1.897947243257748</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.818119281971821</v>
+        <v>1.815141535811144</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.014415786787864</v>
+        <v>-6.928158257591476</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1513862662575485</v>
+        <v>0.1858892779361039</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.892984332989953</v>
+        <v>-1.897947243257748</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.82171840549247</v>
+        <v>1.818740659331793</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.94093587793585</v>
+        <v>-6.854678348739462</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1941057358529079</v>
+        <v>0.2286087475314629</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.819504424137939</v>
+        <v>-1.824467334405733</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.879133856858232</v>
+        <v>1.876156110697556</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.715902878267027</v>
+        <v>-6.629645349070639</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.283139413336734</v>
+        <v>0.3176424250152889</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.594471424469116</v>
+        <v>-1.599434334736911</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.013174134275823</v>
+        <v>2.010196388115146</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.50126850063062</v>
+        <v>-6.415010971434232</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.373687965445614</v>
+        <v>0.408190977124169</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.379837046832709</v>
+        <v>-1.384799957100504</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.146649561911984</v>
+        <v>2.143671815751307</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.234668143656268</v>
+        <v>-6.14841061445988</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4615223670191502</v>
+        <v>0.4960253786977056</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.379837046832709</v>
+        <v>-1.384799957100504</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.12784382069578</v>
+        <v>2.124866074535103</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.994237646851408</v>
+        <v>-5.90798011765502</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5594376423659719</v>
+        <v>0.5939406540445269</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.139406550027849</v>
+        <v>-1.144369460295644</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.273845195403573</v>
+        <v>2.270867449242897</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.751446839201963</v>
+        <v>-5.665189310005575</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6604832792605704</v>
+        <v>0.6949862909391253</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.139406550027849</v>
+        <v>-1.144369460295644</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.277774509238394</v>
+        <v>2.274796763077717</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.635506989576777</v>
+        <v>-5.549249460380389</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7075378030279844</v>
+        <v>0.7420408147065394</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.062584819011725</v>
+        <v>-1.06754772927952</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.324546131765408</v>
+        <v>2.321568385604731</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.392851401153614</v>
+        <v>-5.306593871957226</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8015981096172435</v>
+        <v>0.8361011212957985</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.062584819011725</v>
+        <v>-1.06754772927952</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.321544202985401</v>
+        <v>2.318566456824724</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.172830603116603</v>
+        <v>-5.086573073920215</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8911854658426619</v>
+        <v>0.9256884775212169</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9213649739437451</v>
+        <v>-0.9263278842115394</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.407855147036804</v>
+        <v>2.404877400876127</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.973581973211794</v>
+        <v>-4.887324444015406</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9867791006064086</v>
+        <v>1.021282112284964</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9213649739437451</v>
+        <v>-0.9263278842115394</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.423749329838627</v>
+        <v>2.42077158367795</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.814066869692424</v>
+        <v>-4.727809340496036</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.051730986454458</v>
+        <v>1.086233998133014</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7618498704243751</v>
+        <v>-0.7668127806921695</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.520604236390551</v>
+        <v>2.517626490229874</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.669394724592687</v>
+        <v>-4.583137195396299</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.119687947055793</v>
+        <v>1.154190958734348</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6171777253246378</v>
+        <v>-0.6221406355924322</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.617495626011833</v>
+        <v>2.614517879851156</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.651625265661731</v>
+        <v>-4.565367736465343</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.042135422714897</v>
+        <v>1.076638434393452</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5994082663936822</v>
+        <v>-0.6043711766614766</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.543496993457128</v>
+        <v>2.540519247296451</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.564825767882722</v>
+        <v>-4.478568238686334</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.099255715149067</v>
+        <v>1.133758726827622</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5994082663936822</v>
+        <v>-0.6043711766614766</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.565897486779694</v>
+        <v>2.562919740619017</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.46513315315371</v>
+        <v>-4.378875623957322</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.139205162414084</v>
+        <v>1.173708174092639</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4997156516646704</v>
+        <v>-0.5046785619324647</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.625785456990513</v>
+        <v>2.622807710829837</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.53350333947772</v>
+        <v>-4.447245810281332</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.122864010359182</v>
+        <v>1.157367022037737</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4904399526284555</v>
+        <v>-0.4954028628962498</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.642357798886944</v>
+        <v>2.639380052726267</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.412086909851244</v>
+        <v>-4.325829380654856</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.161867290841664</v>
+        <v>1.196370302520219</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4904399526284555</v>
+        <v>-0.4954028628962498</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.632794507518835</v>
+        <v>2.629816761358159</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.443080069179949</v>
+        <v>-4.356822539983561</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9741795921505685</v>
+        <v>1.008682603829123</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4904399526284555</v>
+        <v>-0.4954028628962498</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.457504072559222</v>
+        <v>2.454526326398546</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.267605809387479</v>
+        <v>-4.181348280191092</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.048936528059344</v>
+        <v>1.083439539737899</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4904399526284555</v>
+        <v>-0.4954028628962498</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.46207130455101</v>
+        <v>2.459093558390333</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.378542062028728</v>
+        <v>-4.29228453283234</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.004573500889642</v>
+        <v>1.039076512568197</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4904399526284555</v>
+        <v>-0.4954028628962498</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.462082778437808</v>
+        <v>2.459105032277131</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.581568639571961</v>
+        <v>-4.495311110375574</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9264942550922544</v>
+        <v>0.9609972667708093</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6934665301716889</v>
+        <v>-0.6984294404394833</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.343398217131773</v>
+        <v>2.340420470971096</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.423643040636668</v>
+        <v>-4.337385511440281</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9998368810985039</v>
+        <v>1.034339892777059</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6934665301716889</v>
+        <v>-0.6984294404394833</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.353570603563905</v>
+        <v>2.350592857403229</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.446164917740473</v>
+        <v>3.794598672774152</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.563211637559666</v>
+        <v>2.768718988979918</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.423643040636668</v>
+        <v>-4.337385511440281</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9998368810985039</v>
+        <v>1.034339892777059</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6934665301716889</v>
+        <v>-0.6984294404394833</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.556275434546034</v>
+        <v>2.761782785966286</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240423.xlsx
+++ b/tame_output/ON/bt/strategyON_20240423.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>28.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-36.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-52.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-80.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.2%</t>
+          <t>117.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.5%</t>
+          <t>137.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-706.9%</t>
+          <t>-707.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>428.8%</t>
+          <t>424.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-595.3%</t>
+          <t>-597.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-272.8%</t>
+          <t>-291.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-38.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-343.8%</t>
+          <t>-360.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.2%</t>
+          <t>-175.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-293.8%</t>
+          <t>-323.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-206.6%</t>
+          <t>-216.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-169.8%</t>
+          <t>-246.9%</t>
         </is>
       </c>
     </row>
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.3818549727391262</v>
+        <v>0.5450498276701428</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.270386615547305</v>
+        <v>3.335664557519712</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.664946924712625</v>
+        <v>1.659272487791352</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.116969205592977</v>
+        <v>4.113564543440213</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,22 +43796,22 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279815</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.1992695863449189</v>
+        <v>0.3630432643471742</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.197841599715496</v>
+        <v>3.263351070916398</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.664946924712625</v>
+        <v>1.659272487791352</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.117458344318852</v>
+        <v>4.114053682166087</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1510473194978354</v>
+        <v>0.1505715702313155</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.18263267559833</v>
+        <v>3.182442375891722</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.616724657865542</v>
+        <v>1.446800793675493</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.092604966832268</v>
+        <v>3.990650648318239</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.0860841723519597</v>
+        <v>-0.08655992161847964</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.122721163355953</v>
+        <v>3.122530863649345</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.616724657865542</v>
+        <v>1.446800793675493</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.127546051329809</v>
+        <v>4.025591732815781</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998562</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.08104658162437317</v>
+        <v>-0.08152233089089311</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.123313639832326</v>
+        <v>3.123123340125718</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.672369114131859</v>
+        <v>1.50244524994181</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.159510165274938</v>
+        <v>4.057555846760909</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2436726615890117</v>
+        <v>-0.2441484108555317</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.037009589470208</v>
+        <v>3.0368192897636</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.50974303416722</v>
+        <v>1.339819169977172</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.040680898919891</v>
+        <v>3.938726580405863</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757924</v>
+        <v>3.293490533757925</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3094400516384238</v>
+        <v>-0.3099158009049438</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.011720242580913</v>
+        <v>3.011529942874305</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.50974303416722</v>
+        <v>1.339819169977172</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.041698508050362</v>
+        <v>3.939744189536333</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.293766719760743</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3229755354151334</v>
+        <v>-0.3234512846816534</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.996934081057985</v>
+        <v>2.996743781351377</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.50974303416722</v>
+        <v>1.339819169977172</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.032326540038118</v>
+        <v>3.930372221524088</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706673</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.4047474358428851</v>
+        <v>-0.405223185109405</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.954308046842122</v>
+        <v>2.954117747135514</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.536778607573357</v>
+        <v>1.366854743383308</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.038630610037038</v>
+        <v>3.936676291523009</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.4719565437147628</v>
+        <v>-0.4724322929812827</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.932189720527073</v>
+        <v>2.931999420820465</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.536778607573357</v>
+        <v>1.366854743383308</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.04339592687074</v>
+        <v>3.941441608356711</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.6795223281063747</v>
+        <v>-0.6799980773728946</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.846988202889669</v>
+        <v>2.846797903183061</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.329212823181745</v>
+        <v>1.159288958991696</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.916681252355014</v>
+        <v>3.814726933840984</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.097276351653212</v>
+        <v>-1.097752100919732</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.677813484975998</v>
+        <v>2.677623185269389</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9114587996349081</v>
+        <v>0.7415349354448594</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.663955729731974</v>
+        <v>3.562001411217945</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.318898285211329</v>
+        <v>-1.319374034477849</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.589030928151672</v>
+        <v>2.588840628445064</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.873932665947539</v>
+        <v>0.7040088017574904</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.641306266118475</v>
+        <v>3.539351947604445</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.526902343564406</v>
+        <v>-1.527378092830926</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.510721449364366</v>
+        <v>2.510531149657758</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.873932665947539</v>
+        <v>0.7040088017574904</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.6461984106724</v>
+        <v>3.544244092158371</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.738314764452381</v>
+        <v>-1.738790513718901</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.421237937347165</v>
+        <v>2.421047637640557</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.662520245059564</v>
+        <v>0.4925963808695153</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.514432414477603</v>
+        <v>3.412478095963574</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.077473142040904</v>
+        <v>-2.077948891307424</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.278658885618205</v>
+        <v>2.278468585911597</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3233618674710419</v>
+        <v>0.1534380032809932</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.304021687230939</v>
+        <v>3.20206736871691</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.405490363768383</v>
+        <v>-2.405966113034903</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.167790286665982</v>
+        <v>2.167599986959374</v>
       </c>
       <c r="F1852" t="n">
-        <v>-0.004655354256437261</v>
+        <v>-0.1745792184464859</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.12754964393322</v>
+        <v>3.025595325419191</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.898815235303561</v>
+        <v>-2.899290984570081</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.978559088460479</v>
+        <v>1.978368788753871</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.109641468496056</v>
+        <v>-0.2795653326861047</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.072656725798017</v>
+        <v>2.970702407283988</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.391200263327658</v>
+        <v>-3.391676012594178</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.782711469294572</v>
+        <v>1.782521169587964</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.6020264965201527</v>
+        <v>-0.7719503607102014</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.778332101027291</v>
+        <v>2.676377782513262</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.77638065425773</v>
+        <v>-3.77685640352425</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.627181851735406</v>
+        <v>1.626991552028799</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.6020264965201527</v>
+        <v>-0.7719503607102014</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.776874639840154</v>
+        <v>2.674920321326125</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.120063427484393</v>
+        <v>-4.120539176750913</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.491477865899358</v>
+        <v>1.49128756619275</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.7099325485473709</v>
+        <v>-0.8798564127374195</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.71390013207844</v>
+        <v>2.611945813564411</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.477713777722741</v>
+        <v>-4.478189526989261</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.344523784460276</v>
+        <v>1.344333484753668</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.067582898785719</v>
+        <v>-1.237506762975768</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.495415980591689</v>
+        <v>2.39346166207766</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.786947880718792</v>
+        <v>-4.787423629985311</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.222603069962116</v>
+        <v>1.222412770255508</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.067582898785719</v>
+        <v>-1.237506762975768</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.497188907291948</v>
+        <v>2.395234588777919</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.218753673868579</v>
+        <v>-5.219229423135099</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.036213640169605</v>
+        <v>1.036023340462997</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.204000395226986</v>
+        <v>-1.373924259417035</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.401671296894593</v>
+        <v>2.299716978380563</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.453447668001131</v>
+        <v>-5.453923417267651</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9306208175186748</v>
+        <v>0.9304305178120669</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.197664127997731</v>
+        <v>-1.367587992187779</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.393757832234237</v>
+        <v>2.291803513720207</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.789110315231584</v>
+        <v>-5.789586064498104</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7949363502824589</v>
+        <v>0.794746050575851</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.197664127997731</v>
+        <v>-1.367587992187779</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.392338423890202</v>
+        <v>2.290384105376172</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.152736560131897</v>
+        <v>-6.153212309398417</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.655973412556575</v>
+        <v>0.6557831128499672</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.295885764864857</v>
+        <v>-1.465809629054905</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.339893002004167</v>
+        <v>2.237938683490138</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.517863942770644</v>
+        <v>-6.518339692037164</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5091769745069077</v>
+        <v>0.5089866748002998</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.592196549163869</v>
+        <v>-1.762120413353918</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.161361046430592</v>
+        <v>2.059406727916563</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.926452719951323</v>
+        <v>-6.926928469217842</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3445030076493953</v>
+        <v>0.3443127079427875</v>
       </c>
       <c r="F1864" t="n">
-        <v>-2.000785326344547</v>
+        <v>-2.170709190534596</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.914969324136943</v>
+        <v>1.813015005622914</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.339435204092417</v>
+        <v>-7.339910953358936</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1744954464644182</v>
+        <v>0.1743051467578107</v>
       </c>
       <c r="F1865" t="n">
-        <v>-2.000785326344547</v>
+        <v>-2.170709190534596</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.910154756608404</v>
+        <v>1.808200438094375</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.755827078379414</v>
+        <v>-7.756302827645933</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.005932747358496471</v>
+        <v>0.005742447651889027</v>
       </c>
       <c r="F1866" t="n">
-        <v>-2.000785326344547</v>
+        <v>-2.170709190534596</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.908148807217281</v>
+        <v>1.806194488703252</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.132504088909258</v>
+        <v>-8.132979838175777</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1344793661847619</v>
+        <v>-0.1346696658913693</v>
       </c>
       <c r="F1867" t="n">
-        <v>-2.000785326344547</v>
+        <v>-2.170709190534596</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.91840749788596</v>
+        <v>1.816453179371931</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.478378910894067</v>
+        <v>-8.478854660160586</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2767297298329905</v>
+        <v>-0.2769200295395979</v>
       </c>
       <c r="F1868" t="n">
-        <v>-2.000785326344547</v>
+        <v>-2.170709190534596</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.914507063031656</v>
+        <v>1.812552744517627</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.64052118135716</v>
+        <v>-8.640996930623679</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3431817179632266</v>
+        <v>-0.3433720176698341</v>
       </c>
       <c r="F1869" t="n">
-        <v>-2.000785326344547</v>
+        <v>-2.170709190534596</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.912911983086657</v>
+        <v>1.810957664572628</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.937182523167358</v>
+        <v>-8.937658272433877</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4580672787580977</v>
+        <v>-0.4582575784647052</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.069528462078426</v>
+        <v>-2.239452326268475</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.875445077575538</v>
+        <v>1.773490759061508</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.370531631277593</v>
+        <v>-9.371007380544112</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6354332265365947</v>
+        <v>-0.6356235262432026</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.069528462078426</v>
+        <v>-2.239452326268475</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.871418773041135</v>
+        <v>1.769464454527105</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.753533020020225</v>
+        <v>-9.754008769286743</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7887358833552316</v>
+        <v>-0.788926183061839</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.069528462078426</v>
+        <v>-2.239452326268475</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.871316671719551</v>
+        <v>1.769362353205521</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.910931900233345</v>
+        <v>-9.911407649499864</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8491239194690494</v>
+        <v>-0.8493142191756573</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.226927342291547</v>
+        <v>-2.396851206481596</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.779448859563108</v>
+        <v>1.677494541049078</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.27046222273735</v>
+        <v>-10.27093797200387</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9875857451726002</v>
+        <v>-0.9877760448792072</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.226927342291547</v>
+        <v>-2.396851206481596</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.784799162861158</v>
+        <v>1.682844844347129</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.59686225140236</v>
+        <v>-10.59733800066888</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.110229736681428</v>
+        <v>-1.110420036388036</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.55332737095656</v>
+        <v>-2.723251235146609</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.596875165619328</v>
+        <v>1.494920847105298</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.81601121947656</v>
+        <v>-10.81648696874308</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.194847573289338</v>
+        <v>-1.195037872995945</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.772476339030757</v>
+        <v>-2.942400203220807</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.468427535396578</v>
+        <v>1.366473216882549</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.81232029452015</v>
+        <v>-10.81279604378667</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.193371203306774</v>
+        <v>-1.193561503013381</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.772476339030757</v>
+        <v>-2.942400203220807</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.468427535396578</v>
+        <v>1.366473216882549</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.01657846985001</v>
+        <v>-11.01705421911653</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.269561276320077</v>
+        <v>-1.269751576026684</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.900115283644746</v>
+        <v>-3.070039147834795</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.397357365746827</v>
+        <v>1.295403047232798</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.23461624148119</v>
+        <v>-11.23509199074771</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.352293830488112</v>
+        <v>-1.352484130194719</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.074886051740645</v>
+        <v>-3.244809915930694</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.296977459373724</v>
+        <v>1.195023140859695</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.16114640981374</v>
+        <v>-11.16162215908026</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.307534196327711</v>
+        <v>-1.307724496034319</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.001416220073197</v>
+        <v>-3.171340084263246</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.356431059867614</v>
+        <v>1.254476741353585</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.33627082720028</v>
+        <v>-11.3367465764668</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.363028742534811</v>
+        <v>-1.363219042241419</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.176540637459741</v>
+        <v>-3.34646450164979</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.265911630183205</v>
+        <v>1.163957311669175</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.57072292121477</v>
+        <v>-11.57119867048129</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.464028745042203</v>
+        <v>-1.464219044748811</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.176540637459741</v>
+        <v>-3.34646450164979</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.258692465281609</v>
+        <v>1.156738146767579</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.85852676575201</v>
+        <v>-11.85900251501853</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.585822473631075</v>
+        <v>-1.586012773337683</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.464344481996979</v>
+        <v>-3.634268346187028</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.079337967785289</v>
+        <v>0.97738364927126</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.08835121291584</v>
+        <v>-12.08882696218235</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.676636462658049</v>
+        <v>-1.676826762364656</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.626992019067139</v>
+        <v>-3.796915883257189</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9828652353817495</v>
+        <v>0.8809109168677201</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.3203801326521</v>
+        <v>-12.32085588191862</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.766754301923439</v>
+        <v>-1.766944601630046</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.689004716255563</v>
+        <v>-3.858928580445612</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9483513456978105</v>
+        <v>0.8463970271837811</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.26836461868328</v>
+        <v>-12.2688403679498</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.741957760649512</v>
+        <v>-1.74214806035612</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.689004716255563</v>
+        <v>-3.858928580445612</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9523416813842114</v>
+        <v>0.8503873628701819</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.4100364604074</v>
+        <v>-12.41051220967392</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.800101724237902</v>
+        <v>-1.80029202394451</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.689004716255563</v>
+        <v>-3.858928580445612</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9508664544854697</v>
+        <v>0.8489121359714402</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.50894320086668</v>
+        <v>-12.5094189501332</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.824611010256741</v>
+        <v>-1.824801309963348</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.787911456714838</v>
+        <v>-3.957835320904887</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9065758203747762</v>
+        <v>0.8046215018607468</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.30979109362958</v>
+        <v>-12.3102668428961</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.758001301008584</v>
+        <v>-1.758191600715192</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.622588930765025</v>
+        <v>-3.792512794955074</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9927182022979815</v>
+        <v>0.890763883783952</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.08394594091017</v>
+        <v>-12.08442169017669</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.65808416688461</v>
+        <v>-1.658274466591219</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.580662255177861</v>
+        <v>-3.75058611936791</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.027453280686488</v>
+        <v>0.9254989621724588</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.79767112858747</v>
+        <v>-11.79814687785399</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.542435097399473</v>
+        <v>-1.542625397106082</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.580662255177861</v>
+        <v>-3.75058611936791</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.028592425242547</v>
+        <v>0.9266381067285177</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.85056641663176</v>
+        <v>-11.85104216589828</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.560959438455081</v>
+        <v>-1.561149738161689</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.575706909089415</v>
+        <v>-3.745630773279464</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.034199407057722</v>
+        <v>0.9322450885436928</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.56665768570301</v>
+        <v>-11.56713343496953</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.441662241844944</v>
+        <v>-1.441852541551553</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.575706909089415</v>
+        <v>-3.745630773279464</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.039933111296359</v>
+        <v>0.9379787927823293</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.45123676156492</v>
+        <v>-11.45171251083144</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.405231134583572</v>
+        <v>-1.405421434290179</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.460285984951319</v>
+        <v>-3.630209849141369</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.099448403385351</v>
+        <v>0.9974940848713216</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.18739989436085</v>
+        <v>-11.18787564362737</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.309579869014851</v>
+        <v>-1.309770168721459</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.460285984951319</v>
+        <v>-3.630209849141369</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.089564922072443</v>
+        <v>0.987610603558414</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.92015809349245</v>
+        <v>-10.92063384275897</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.204517709166865</v>
+        <v>-1.204708008873474</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.460285984951319</v>
+        <v>-3.630209849141369</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.08773036157307</v>
+        <v>0.9857760430590403</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.79685216501423</v>
+        <v>-10.79732791428075</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.155495652749039</v>
+        <v>-1.155685952455647</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.370868313823757</v>
+        <v>-3.540792178013806</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.141080649276147</v>
+        <v>1.039126330762117</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.77289862403827</v>
+        <v>-10.77337437330479</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.145245730213162</v>
+        <v>-1.14543602991977</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.346914772847799</v>
+        <v>-3.516838637037848</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.156121280007215</v>
+        <v>1.054166961493185</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.50883868571547</v>
+        <v>-10.509314434982</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.052882071045795</v>
+        <v>-1.053072370752403</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.082854834525003</v>
+        <v>-3.252778698715052</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.301296926839141</v>
+        <v>1.199342608325111</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.801759062210637</v>
+        <v>-9.802234811477158</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7728372553041614</v>
+        <v>-0.7730275550107697</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.082854834525003</v>
+        <v>-3.252778698715052</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.29850989317884</v>
+        <v>1.19655557466481</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.761574763844447</v>
+        <v>-9.762050513110967</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7564199120698438</v>
+        <v>-0.7566102117764522</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.042670536158812</v>
+        <v>-3.212594400348861</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.322964096086396</v>
+        <v>1.221009777572366</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.681504968306642</v>
+        <v>-9.681980717573163</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7250251726339649</v>
+        <v>-0.7252154723405733</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.962600740621008</v>
+        <v>-3.132524604811057</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.370372794629835</v>
+        <v>1.268418476115805</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.448023746077045</v>
+        <v>-9.448499495343565</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6237082549042734</v>
+        <v>-0.6238985546108817</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.729119518391409</v>
+        <v>-2.899043382581458</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.518385956805447</v>
+        <v>1.416431638291417</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.268315215933171</v>
+        <v>-9.268790965199692</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5547170531596834</v>
+        <v>-0.5549073528662918</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.671948014228713</v>
+        <v>-2.841871878418762</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.549796648990105</v>
+        <v>1.447842330476075</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.136039742302284</v>
+        <v>-9.136515491568804</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5064393769603015</v>
+        <v>-0.5066296766669098</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.539672540597827</v>
+        <v>-2.709596404787876</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.624529419915664</v>
+        <v>1.522575101401634</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.94544006762913</v>
+        <v>-8.945915816895651</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4273844464034031</v>
+        <v>-0.4275747461100114</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.349072865924674</v>
+        <v>-2.518996730114723</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.741704285407192</v>
+        <v>1.639749966893163</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.696440268945549</v>
+        <v>-8.69691601821207</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3148781857063123</v>
+        <v>-0.3150684854129202</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.349072865924674</v>
+        <v>-2.518996730114723</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.754610626630851</v>
+        <v>1.652656308116821</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.802030258718654</v>
+        <v>-8.802506007985174</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4850901112147725</v>
+        <v>-0.4852804109213809</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.454662855697779</v>
+        <v>-2.624586719887828</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.563280703167769</v>
+        <v>1.46132638465374</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.820765160837251</v>
+        <v>-8.821240910103771</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4440397301851249</v>
+        <v>-0.4442300298917332</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.454662855697779</v>
+        <v>-2.624586719887828</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.611825045044856</v>
+        <v>1.509870726530826</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.672825119429652</v>
+        <v>-8.673300868696172</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5047426363102527</v>
+        <v>-0.5049329360168611</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.434341939789221</v>
+        <v>-2.60426580397927</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.504138671901823</v>
+        <v>1.402184353387793</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.545932712994581</v>
+        <v>-8.546408462261102</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4626996599897031</v>
+        <v>-0.4628899596963114</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.307449533354151</v>
+        <v>-2.4773733975442</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.571560129509386</v>
+        <v>1.469605810995357</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568104</v>
+        <v>3.729966140568103</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.50238430622389</v>
+        <v>-8.502860055490411</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4522409093765196</v>
+        <v>-0.4524312090831279</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.307449533354151</v>
+        <v>-2.4773733975442</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.564599517414293</v>
+        <v>1.462645198900264</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.260235912770032</v>
+        <v>-8.260711662036552</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3409191976138333</v>
+        <v>-0.3411094973204416</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.307449533354151</v>
+        <v>-2.4773733975442</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.579061871795436</v>
+        <v>1.477107553281407</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.197006541001684</v>
+        <v>-8.197482290268205</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3210953284472993</v>
+        <v>-0.3212856281539076</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.307449533354151</v>
+        <v>-2.4773733975442</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.573593992254631</v>
+        <v>1.471639673740602</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.010518848624677</v>
+        <v>-8.010994597891198</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2490021574859198</v>
+        <v>-0.2491924571925277</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.120961840977145</v>
+        <v>-2.290885705167194</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.682984701691412</v>
+        <v>1.581030383177383</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.989369649721234</v>
+        <v>-7.989845398987755</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.232841499687217</v>
+        <v>-0.2330317993938253</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.099812642073701</v>
+        <v>-2.26973650626375</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.703375199270803</v>
+        <v>1.601420880756774</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.74560420773779</v>
+        <v>-7.74607995700431</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1395546145467885</v>
+        <v>-0.1397449142533969</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.099812642073701</v>
+        <v>-2.26973650626375</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.699155907617854</v>
+        <v>1.597201589103825</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.481576140544529</v>
+        <v>-7.48205188981105</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.03181907374946835</v>
+        <v>-0.03200937345607668</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.897947243257748</v>
+        <v>-2.067871107447797</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.822399460827442</v>
+        <v>1.720445142313413</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.231725746595455</v>
+        <v>-7.232201495861975</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.06086315881386328</v>
+        <v>0.06067285910725539</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.897947243257748</v>
+        <v>-2.067871107447797</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.815141535811144</v>
+        <v>1.713187217297115</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.928158257591476</v>
+        <v>-6.928634006857997</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1858892779361039</v>
+        <v>0.1856989782294955</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.897947243257748</v>
+        <v>-2.067871107447797</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.818740659331793</v>
+        <v>1.716786340817763</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.854678348739462</v>
+        <v>-6.855154098005983</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2286087475314629</v>
+        <v>0.2284184478248545</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.824467334405733</v>
+        <v>-1.994391198595783</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.876156110697556</v>
+        <v>1.774201792183526</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.629645349070639</v>
+        <v>-6.63012109833716</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3176424250152889</v>
+        <v>0.3174521253086811</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.599434334736911</v>
+        <v>-1.76935819892696</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.010196388115146</v>
+        <v>1.908242069601117</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.415010971434232</v>
+        <v>-6.415486720700753</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.408190977124169</v>
+        <v>0.4080006774175611</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.384799957100504</v>
+        <v>-1.554723821290553</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.143671815751307</v>
+        <v>2.041717497237278</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.14841061445988</v>
+        <v>-6.148886363726401</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4960253786977056</v>
+        <v>0.4958350789910972</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.384799957100504</v>
+        <v>-1.554723821290553</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.124866074535103</v>
+        <v>2.022911756021073</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.90798011765502</v>
+        <v>-5.908455866921541</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5939406540445269</v>
+        <v>0.593750354337919</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.144369460295644</v>
+        <v>-1.314293324485693</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.270867449242897</v>
+        <v>2.168913130728867</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.665189310005575</v>
+        <v>-5.665665059272095</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6949862909391253</v>
+        <v>0.694795991232517</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.144369460295644</v>
+        <v>-1.314293324485693</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.274796763077717</v>
+        <v>2.172842444563687</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.549249460380389</v>
+        <v>-5.54972520964691</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7420408147065394</v>
+        <v>0.7418505149999315</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.06754772927952</v>
+        <v>-1.237471593469569</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.321568385604731</v>
+        <v>2.219614067090702</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.306593871957226</v>
+        <v>-5.307069621223746</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8361011212957985</v>
+        <v>0.8359108215891902</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.06754772927952</v>
+        <v>-1.237471593469569</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.318566456824724</v>
+        <v>2.216612138310695</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.086573073920215</v>
+        <v>-5.087048823186736</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9256884775212169</v>
+        <v>0.9254981778146085</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9263278842115394</v>
+        <v>-1.096251748401589</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.404877400876127</v>
+        <v>2.302923082362097</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.887324444015406</v>
+        <v>-4.887800193281927</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.021282112284964</v>
+        <v>1.021091812578355</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9263278842115394</v>
+        <v>-1.096251748401589</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.42077158367795</v>
+        <v>2.318817265163921</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.727809340496036</v>
+        <v>-4.728285089762557</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.086233998133014</v>
+        <v>1.086043698426405</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7668127806921695</v>
+        <v>-0.9367366448822186</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.517626490229874</v>
+        <v>2.415672171715844</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.583137195396299</v>
+        <v>-4.58361294466282</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.154190958734348</v>
+        <v>1.15400065902774</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6221406355924322</v>
+        <v>-0.7920644997824813</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.614517879851156</v>
+        <v>2.512563561337127</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.565367736465343</v>
+        <v>-4.694533210670747</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.076638434393452</v>
+        <v>1.024972244711291</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6043711766614766</v>
+        <v>-0.9029847657904089</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.540519247296451</v>
+        <v>2.361351093819092</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.478568238686334</v>
+        <v>-4.607733712891738</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.133758726827622</v>
+        <v>1.08209253714546</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6043711766614766</v>
+        <v>-0.9029847657904089</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.562919740619017</v>
+        <v>2.383751587141658</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.378875623957322</v>
+        <v>-4.508041098162726</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.173708174092639</v>
+        <v>1.122041984410477</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5046785619324647</v>
+        <v>-0.8032921510613971</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.622807710829837</v>
+        <v>2.443639557352477</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.447245810281332</v>
+        <v>-4.576411284486737</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.157367022037737</v>
+        <v>1.105700832355575</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4954028628962498</v>
+        <v>-0.7940164520251821</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.639380052726267</v>
+        <v>2.460211899248908</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.325829380654856</v>
+        <v>-4.45499485486026</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.196370302520219</v>
+        <v>1.144704112838057</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4954028628962498</v>
+        <v>-0.7940164520251821</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.629816761358159</v>
+        <v>2.4506486078808</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.356822539983561</v>
+        <v>-4.485988014188965</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.008682603829123</v>
+        <v>0.9570164141469619</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4954028628962498</v>
+        <v>-0.7940164520251821</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.454526326398546</v>
+        <v>2.275358172921186</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.181348280191092</v>
+        <v>-4.310513754396496</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.083439539737899</v>
+        <v>1.031773350055738</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4954028628962498</v>
+        <v>-0.7940164520251821</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.459093558390333</v>
+        <v>2.279925404912974</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.29228453283234</v>
+        <v>-4.421450007037745</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.039076512568197</v>
+        <v>0.9874103228860354</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4954028628962498</v>
+        <v>-0.7940164520251821</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.459105032277131</v>
+        <v>2.279936878799772</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.495311110375574</v>
+        <v>-4.624476584580978</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9609972667708093</v>
+        <v>0.9093310770886478</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6984294404394833</v>
+        <v>-0.9970430295684155</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.340420470971096</v>
+        <v>2.161252317493737</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.337385511440281</v>
+        <v>-4.466550985645685</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.034339892777059</v>
+        <v>0.9826737030948973</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6984294404394833</v>
+        <v>-0.9970430295684155</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.350592857403229</v>
+        <v>2.17142470392587</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.794598672774152</v>
+        <v>3.56479303264555</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.768718988979918</v>
+        <v>2.58920188715285</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.337385511440281</v>
+        <v>-4.35651960863218</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.034339892777059</v>
+        <v>0.8462376193862307</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6984294404394833</v>
+        <v>-0.9970430295684155</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.761782785966286</v>
+        <v>1.990976069411801</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240423.xlsx
+++ b/tame_output/ON/bt/strategyON_20240423.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>20.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-36.8%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-52.7%</t>
+          <t>-35.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.3%</t>
+          <t>116.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.4%</t>
+          <t>136.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-707.0%</t>
+          <t>-690.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.1%</t>
+          <t>-57.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>424.0%</t>
+          <t>372.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-597.2%</t>
+          <t>-580.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.2%</t>
+          <t>-276.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,47 +1150,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.4%</t>
+          <t>-44.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-291.6%</t>
+          <t>-267.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-38.6%</t>
+          <t>-36.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-360.8%</t>
+          <t>-344.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-175.7%</t>
+          <t>-167.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-323.7%</t>
+          <t>-305.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-216.8%</t>
+          <t>-207.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-246.9%</t>
+          <t>-218.6%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279815</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1505715702313155</v>
+        <v>0.3148209975000906</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.182442375891722</v>
+        <v>3.248142146799232</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.446800793675493</v>
+        <v>1.611050220944268</v>
       </c>
       <c r="G1838" t="n">
-        <v>3.990650648318239</v>
+        <v>4.089200304679504</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.08655992161847964</v>
+        <v>0.07768950565029553</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.122530863649345</v>
+        <v>3.188230634556855</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.446800793675493</v>
+        <v>1.611050220944268</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.025591732815781</v>
+        <v>4.124141389177046</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.08152233089089311</v>
+        <v>0.08272709637788206</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.123123340125718</v>
+        <v>3.188823111033228</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.50244524994181</v>
+        <v>1.666694677210586</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.057555846760909</v>
+        <v>4.156105503122173</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2441484108555317</v>
+        <v>-0.07989898358675651</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.0368192897636</v>
+        <v>3.102519060671109</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.339819169977172</v>
+        <v>1.504068597245947</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.938726580405863</v>
+        <v>4.037276236767128</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757925</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3099158009049438</v>
+        <v>-0.1456663736361686</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.011529942874305</v>
+        <v>3.077229713781815</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.339819169977172</v>
+        <v>1.504068597245947</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.939744189536333</v>
+        <v>4.038293845897598</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3234512846816534</v>
+        <v>-0.1592018574128782</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.996743781351377</v>
+        <v>3.062443552258887</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.339819169977172</v>
+        <v>1.504068597245947</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.930372221524088</v>
+        <v>4.028921877885353</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.405223185109405</v>
+        <v>-0.2409737578406299</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.954117747135514</v>
+        <v>3.019817518043024</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.366854743383308</v>
+        <v>1.531104170652084</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.936676291523009</v>
+        <v>4.035225947884274</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.4724322929812827</v>
+        <v>-0.3081828657125075</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.931999420820465</v>
+        <v>2.997699191727976</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.366854743383308</v>
+        <v>1.531104170652084</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.941441608356711</v>
+        <v>4.039991264717976</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.6799980773728946</v>
+        <v>-0.5157486501041194</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.846797903183061</v>
+        <v>2.912497674090571</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.159288958991696</v>
+        <v>1.323538386260472</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.814726933840984</v>
+        <v>3.913276590202249</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.097752100919732</v>
+        <v>-0.9335026736509564</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.677623185269389</v>
+        <v>2.743322956176899</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.7415349354448594</v>
+        <v>0.9057843627136347</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.562001411217945</v>
+        <v>3.660551067579211</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.319374034477849</v>
+        <v>-1.155124607209074</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.588840628445064</v>
+        <v>2.654540399352574</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.7040088017574904</v>
+        <v>0.8682582290262657</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.539351947604445</v>
+        <v>3.637901603965711</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.527378092830926</v>
+        <v>-1.363128665562151</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.510531149657758</v>
+        <v>2.576230920565269</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.7040088017574904</v>
+        <v>0.8682582290262657</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.544244092158371</v>
+        <v>3.642793748519636</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.738790513718901</v>
+        <v>-1.574541086450126</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.421047637640557</v>
+        <v>2.486747408548067</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.4925963808695153</v>
+        <v>0.6568458081382906</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.412478095963574</v>
+        <v>3.511027752324839</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.077948891307424</v>
+        <v>-1.913699464038648</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.278468585911597</v>
+        <v>2.344168356819107</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.1534380032809932</v>
+        <v>0.3176874305497686</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.20206736871691</v>
+        <v>3.300617025078175</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.405966113034903</v>
+        <v>-2.241716685766128</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.167599986959374</v>
+        <v>2.233299757866884</v>
       </c>
       <c r="F1852" t="n">
-        <v>-0.1745792184464859</v>
+        <v>-0.0103297911777106</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.025595325419191</v>
+        <v>3.124144981780456</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.899290984570081</v>
+        <v>-2.735041557301306</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.978368788753871</v>
+        <v>2.044068559661381</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.2795653326861047</v>
+        <v>-0.1153159054173293</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.970702407283988</v>
+        <v>3.069252063645253</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.391676012594178</v>
+        <v>-3.227426585325403</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.782521169587964</v>
+        <v>1.848220940495474</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.7719503607102014</v>
+        <v>-0.6077009334414261</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.676377782513262</v>
+        <v>2.774927438874527</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.77685640352425</v>
+        <v>-3.612606976255475</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.626991552028799</v>
+        <v>1.692691322936309</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.7719503607102014</v>
+        <v>-0.6077009334414261</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.674920321326125</v>
+        <v>2.773469977687391</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.120539176750913</v>
+        <v>-3.956289749482138</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.49128756619275</v>
+        <v>1.55698733710026</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.8798564127374195</v>
+        <v>-0.7156069854686442</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.611945813564411</v>
+        <v>2.710495469925676</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.478189526989261</v>
+        <v>-4.313940099720486</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.344333484753668</v>
+        <v>1.410033255661178</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.237506762975768</v>
+        <v>-1.073257335706992</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.39346166207766</v>
+        <v>2.492011318438925</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.787423629985311</v>
+        <v>-4.623174202716537</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.222412770255508</v>
+        <v>1.288112541163017</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.237506762975768</v>
+        <v>-1.073257335706992</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.395234588777919</v>
+        <v>2.493784245139184</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.219229423135099</v>
+        <v>-5.054979995866324</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.036023340462997</v>
+        <v>1.101723111370507</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.373924259417035</v>
+        <v>-1.209674832148259</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.299716978380563</v>
+        <v>2.398266634741828</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.453923417267651</v>
+        <v>-5.289673989998876</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9304305178120669</v>
+        <v>0.9961302887195767</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.367587992187779</v>
+        <v>-1.203338564919004</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.291803513720207</v>
+        <v>2.390353170081473</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.789586064498104</v>
+        <v>-5.625336637229329</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.794746050575851</v>
+        <v>0.8604458214833608</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.367587992187779</v>
+        <v>-1.203338564919004</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.290384105376172</v>
+        <v>2.388933761737437</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.153212309398417</v>
+        <v>-5.988962882129642</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6557831128499672</v>
+        <v>0.7214828837574769</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.465809629054905</v>
+        <v>-1.30156020178613</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.237938683490138</v>
+        <v>2.336488339851404</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.518339692037164</v>
+        <v>-6.354090264768389</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5089866748002998</v>
+        <v>0.5746864457078096</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.762120413353918</v>
+        <v>-1.597870986085142</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.059406727916563</v>
+        <v>2.157956384277828</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.926928469217842</v>
+        <v>-6.762679041949067</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3443127079427875</v>
+        <v>0.4100124788502977</v>
       </c>
       <c r="F1864" t="n">
-        <v>-2.170709190534596</v>
+        <v>-2.006459763265821</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.813015005622914</v>
+        <v>1.91156466198418</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.339910953358936</v>
+        <v>-7.175661526090161</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1743051467578107</v>
+        <v>0.2400049176653205</v>
       </c>
       <c r="F1865" t="n">
-        <v>-2.170709190534596</v>
+        <v>-2.006459763265821</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.808200438094375</v>
+        <v>1.90675009445564</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.756302827645933</v>
+        <v>-7.592053400377158</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.005742447651889027</v>
+        <v>0.07144221855939925</v>
       </c>
       <c r="F1866" t="n">
-        <v>-2.170709190534596</v>
+        <v>-2.006459763265821</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.806194488703252</v>
+        <v>1.904744145064518</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.132979838175777</v>
+        <v>-7.968730410907003</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1346696658913693</v>
+        <v>-0.06896989498385953</v>
       </c>
       <c r="F1867" t="n">
-        <v>-2.170709190534596</v>
+        <v>-2.006459763265821</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.816453179371931</v>
+        <v>1.915002835733197</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.478854660160586</v>
+        <v>-8.314605232891811</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2769200295395979</v>
+        <v>-0.2112202586320877</v>
       </c>
       <c r="F1868" t="n">
-        <v>-2.170709190534596</v>
+        <v>-2.006459763265821</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.812552744517627</v>
+        <v>1.911102400878891</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.640996930623679</v>
+        <v>-8.476747503354904</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3433720176698341</v>
+        <v>-0.2776722467623243</v>
       </c>
       <c r="F1869" t="n">
-        <v>-2.170709190534596</v>
+        <v>-2.006459763265821</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.810957664572628</v>
+        <v>1.909507320933893</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.937658272433877</v>
+        <v>-8.773408845165102</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4582575784647052</v>
+        <v>-0.3925578075571954</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.239452326268475</v>
+        <v>-2.075202898999699</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.773490759061508</v>
+        <v>1.872040415422774</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.371007380544112</v>
+        <v>-9.206757953275337</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6356235262432026</v>
+        <v>-0.5699237553356924</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.239452326268475</v>
+        <v>-2.075202898999699</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.769464454527105</v>
+        <v>1.868014110888371</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.754008769286743</v>
+        <v>-9.589759342017969</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.788926183061839</v>
+        <v>-0.7232264121543288</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.239452326268475</v>
+        <v>-2.075202898999699</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.769362353205521</v>
+        <v>1.867912009566787</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.911407649499864</v>
+        <v>-9.747158222231089</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8493142191756573</v>
+        <v>-0.7836144482681471</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.396851206481596</v>
+        <v>-2.23260177921282</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.677494541049078</v>
+        <v>1.776044197410344</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.27093797200387</v>
+        <v>-10.10668854473509</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9877760448792072</v>
+        <v>-0.9220762739716974</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.396851206481596</v>
+        <v>-2.23260177921282</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.682844844347129</v>
+        <v>1.781394500708394</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.59733800066888</v>
+        <v>-10.4330885734001</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.110420036388036</v>
+        <v>-1.044720265480525</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.723251235146609</v>
+        <v>-2.559001807877833</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.494920847105298</v>
+        <v>1.593470503466564</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.81648696874308</v>
+        <v>-10.6522375414743</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.195037872995945</v>
+        <v>-1.129338102088436</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.942400203220807</v>
+        <v>-2.778150775952031</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.366473216882549</v>
+        <v>1.465022873243814</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.81279604378667</v>
+        <v>-10.64854661651789</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.193561503013381</v>
+        <v>-1.127861732105871</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.942400203220807</v>
+        <v>-2.778150775952031</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.366473216882549</v>
+        <v>1.465022873243814</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.01705421911653</v>
+        <v>-10.85280479184775</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.269751576026684</v>
+        <v>-1.204051805119175</v>
       </c>
       <c r="F1878" t="n">
-        <v>-3.070039147834795</v>
+        <v>-2.90578972056602</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.295403047232798</v>
+        <v>1.393952703594063</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.23509199074771</v>
+        <v>-11.07084256347893</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.352484130194719</v>
+        <v>-1.286784359287209</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.244809915930694</v>
+        <v>-3.080560488661919</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.195023140859695</v>
+        <v>1.29357279722096</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.16162215908026</v>
+        <v>-10.99737273181148</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.307724496034319</v>
+        <v>-1.242024725126808</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.171340084263246</v>
+        <v>-3.00709065699447</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.254476741353585</v>
+        <v>1.35302639771485</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.3367465764668</v>
+        <v>-11.17249714919803</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.363219042241419</v>
+        <v>-1.297519271333909</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.34646450164979</v>
+        <v>-3.182215074381014</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.163957311669175</v>
+        <v>1.262506968030441</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.57119867048129</v>
+        <v>-11.40694924321252</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.464219044748811</v>
+        <v>-1.398519273841301</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.34646450164979</v>
+        <v>-3.182215074381014</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.156738146767579</v>
+        <v>1.255287803128845</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.85900251501853</v>
+        <v>-11.69475308774975</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.586012773337683</v>
+        <v>-1.520313002430173</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.634268346187028</v>
+        <v>-3.470018918918252</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.97738364927126</v>
+        <v>1.075933305632526</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.08882696218235</v>
+        <v>-11.92457753491358</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.676826762364656</v>
+        <v>-1.611126991457146</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.796915883257189</v>
+        <v>-3.632666455988413</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.8809109168677201</v>
+        <v>0.9794605732289856</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.32085588191862</v>
+        <v>-12.15660645464984</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.766944601630046</v>
+        <v>-1.701244830722537</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.858928580445612</v>
+        <v>-3.694679153176836</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.8463970271837811</v>
+        <v>0.9449466835450462</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.2688403679498</v>
+        <v>-12.10459094068103</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.74214806035612</v>
+        <v>-1.676448289448611</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.858928580445612</v>
+        <v>-3.694679153176836</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.8503873628701819</v>
+        <v>0.948937019231447</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.41051220967392</v>
+        <v>-12.24626278240515</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.80029202394451</v>
+        <v>-1.734592253037</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.858928580445612</v>
+        <v>-3.694679153176836</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.8489121359714402</v>
+        <v>0.9474617923327053</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.5094189501332</v>
+        <v>-12.34516952286442</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.824801309963348</v>
+        <v>-1.759101539055838</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.957835320904887</v>
+        <v>-3.793585893636112</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8046215018607468</v>
+        <v>0.9031711582220123</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.3102668428961</v>
+        <v>-12.14601741562733</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.758191600715192</v>
+        <v>-1.692491829807681</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.792512794955074</v>
+        <v>-3.628263367686298</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.890763883783952</v>
+        <v>0.9893135401452176</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.08442169017669</v>
+        <v>-11.92017226290791</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.658274466591219</v>
+        <v>-1.592574695683708</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.75058611936791</v>
+        <v>-3.586336692099135</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.9254989621724588</v>
+        <v>1.024048618533724</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.79814687785399</v>
+        <v>-11.63389745058522</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.542625397106082</v>
+        <v>-1.476925626198572</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.75058611936791</v>
+        <v>-3.586336692099135</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.9266381067285177</v>
+        <v>1.025187763089783</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.85104216589828</v>
+        <v>-11.68679273862951</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.561149738161689</v>
+        <v>-1.495449967254179</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.745630773279464</v>
+        <v>-3.581381346010688</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.9322450885436928</v>
+        <v>1.030794744904958</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.56713343496953</v>
+        <v>-11.40288400770076</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.441852541551553</v>
+        <v>-1.376152770644043</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.745630773279464</v>
+        <v>-3.581381346010688</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.9379787927823293</v>
+        <v>1.036528449143595</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.45171251083144</v>
+        <v>-11.28746308356266</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.405421434290179</v>
+        <v>-1.33972166338267</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.630209849141369</v>
+        <v>-3.465960421872593</v>
       </c>
       <c r="G1894" t="n">
-        <v>0.9974940848713216</v>
+        <v>1.096043741232587</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.18787564362737</v>
+        <v>-11.02362621635859</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.309770168721459</v>
+        <v>-1.244070397813949</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.630209849141369</v>
+        <v>-3.465960421872593</v>
       </c>
       <c r="G1895" t="n">
-        <v>0.987610603558414</v>
+        <v>1.08616025991968</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.92063384275897</v>
+        <v>-10.75638441549019</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.204708008873474</v>
+        <v>-1.139008237965963</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.630209849141369</v>
+        <v>-3.465960421872593</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.9857760430590403</v>
+        <v>1.084325699420306</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.79732791428075</v>
+        <v>-10.63307848701197</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.155685952455647</v>
+        <v>-1.089986181548137</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.540792178013806</v>
+        <v>-3.37654275074503</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.039126330762117</v>
+        <v>1.137675987123383</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.77337437330479</v>
+        <v>-10.60912494603602</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.14543602991977</v>
+        <v>-1.079736259012261</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.516838637037848</v>
+        <v>-3.352589209769072</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.054166961493185</v>
+        <v>1.152716617854451</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.509314434982</v>
+        <v>-10.34506500771322</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.053072370752403</v>
+        <v>-0.9873725998448935</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.252778698715052</v>
+        <v>-3.088529271446276</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.199342608325111</v>
+        <v>1.297892264686377</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.802234811477158</v>
+        <v>-9.637985384208383</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7730275550107697</v>
+        <v>-0.7073277841032595</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.252778698715052</v>
+        <v>-3.088529271446276</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.19655557466481</v>
+        <v>1.295105231026076</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.762050513110967</v>
+        <v>-9.597801085842192</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7566102117764522</v>
+        <v>-0.6909104408689419</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.212594400348861</v>
+        <v>-3.048344973080085</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.221009777572366</v>
+        <v>1.319559433933632</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.681980717573163</v>
+        <v>-9.517731290304388</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7252154723405733</v>
+        <v>-0.6595157014330635</v>
       </c>
       <c r="F1902" t="n">
-        <v>-3.132524604811057</v>
+        <v>-2.968275177542281</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.268418476115805</v>
+        <v>1.366968132477071</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.448499495343565</v>
+        <v>-9.28425006807479</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6238985546108817</v>
+        <v>-0.5581987837033719</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.899043382581458</v>
+        <v>-2.734793955312683</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.416431638291417</v>
+        <v>1.514981294652682</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.268790965199692</v>
+        <v>-9.104541537930917</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5549073528662918</v>
+        <v>-0.4892075819587816</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.841871878418762</v>
+        <v>-2.677622451149987</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.447842330476075</v>
+        <v>1.546391986837341</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.136515491568804</v>
+        <v>-8.97226606430003</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5066296766669098</v>
+        <v>-0.4409299057593996</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.709596404787876</v>
+        <v>-2.5453469775191</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.522575101401634</v>
+        <v>1.6211247577629</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.945915816895651</v>
+        <v>-8.895375401653498</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4275747461100114</v>
+        <v>-0.4073585800131503</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.518996730114723</v>
+        <v>-2.468456314872567</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.639749966893163</v>
+        <v>1.670074216038456</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.69691601821207</v>
+        <v>-8.646375602969917</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3150684854129202</v>
+        <v>-0.294852319316059</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.518996730114723</v>
+        <v>-2.468456314872567</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.652656308116821</v>
+        <v>1.682980557262115</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.802506007985174</v>
+        <v>-8.751965592743021</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4852804109213809</v>
+        <v>-0.4650642448245197</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.624586719887828</v>
+        <v>-2.574046304645672</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.46132638465374</v>
+        <v>1.491650633799033</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.821240910103771</v>
+        <v>-8.770700494861618</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4442300298917332</v>
+        <v>-0.424013863794872</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.624586719887828</v>
+        <v>-2.574046304645672</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.509870726530826</v>
+        <v>1.54019497567612</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.673300868696172</v>
+        <v>-8.622760453454019</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5049329360168611</v>
+        <v>-0.4847167699199999</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.60426580397927</v>
+        <v>-2.553725388737114</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.402184353387793</v>
+        <v>1.432508602533087</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.546408462261102</v>
+        <v>-8.495868047018948</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4628899596963114</v>
+        <v>-0.4426737935994498</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.4773733975442</v>
+        <v>-2.426832982302044</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.469605810995357</v>
+        <v>1.499930060140651</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.502860055490411</v>
+        <v>-8.452319640248257</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4524312090831279</v>
+        <v>-0.4322150429862663</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.4773733975442</v>
+        <v>-2.426832982302044</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.462645198900264</v>
+        <v>1.492969448045558</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963415</v>
+        <v>3.782918957963414</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.260711662036552</v>
+        <v>-8.210171246794399</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3411094973204416</v>
+        <v>-0.32089333122358</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.4773733975442</v>
+        <v>-2.426832982302044</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.477107553281407</v>
+        <v>1.507431802426701</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192813</v>
+        <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.197482290268205</v>
+        <v>-8.146941875026052</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3212856281539076</v>
+        <v>-0.301069462057046</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.4773733975442</v>
+        <v>-2.426832982302044</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.471639673740602</v>
+        <v>1.501963922885896</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.010994597891198</v>
+        <v>-7.960454182649046</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2491924571925277</v>
+        <v>-0.228976291095667</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.290885705167194</v>
+        <v>-2.240345289925038</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.581030383177383</v>
+        <v>1.611354632322676</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.989845398987755</v>
+        <v>-7.939304983745602</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2330317993938253</v>
+        <v>-0.2128156332969642</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.26973650626375</v>
+        <v>-2.219196091021594</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.601420880756774</v>
+        <v>1.631745129902068</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832483278809</v>
+        <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.74607995700431</v>
+        <v>-7.695539541762158</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1397449142533969</v>
+        <v>-0.1195287481565361</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.26973650626375</v>
+        <v>-2.219196091021594</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.597201589103825</v>
+        <v>1.627525838249118</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527522</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.48205188981105</v>
+        <v>-7.431511474568898</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.03200937345607668</v>
+        <v>-0.01179320735921596</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.067871107447797</v>
+        <v>-2.017330692205641</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.720445142313413</v>
+        <v>1.750769391458706</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.232201495861975</v>
+        <v>-7.181661080619824</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.06067285910725539</v>
+        <v>0.08088902520411567</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.067871107447797</v>
+        <v>-2.017330692205641</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.713187217297115</v>
+        <v>1.743511466442408</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.928634006857997</v>
+        <v>-6.878093591615845</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1856989782294955</v>
+        <v>0.2059151443263563</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.067871107447797</v>
+        <v>-2.017330692205641</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.716786340817763</v>
+        <v>1.747110589963057</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.855154098005983</v>
+        <v>-6.804613682763831</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2284184478248545</v>
+        <v>0.2486346139217153</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.994391198595783</v>
+        <v>-1.943850783353627</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.774201792183526</v>
+        <v>1.804526041328819</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.63012109833716</v>
+        <v>-6.579580683095008</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3174521253086811</v>
+        <v>0.3376682914055413</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.76935819892696</v>
+        <v>-1.718817783684804</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.908242069601117</v>
+        <v>1.93856631874641</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.415486720700753</v>
+        <v>-6.364946305458601</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4080006774175611</v>
+        <v>0.4282168435144214</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.554723821290553</v>
+        <v>-1.504183406048397</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.041717497237278</v>
+        <v>2.072041746382571</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.148886363726401</v>
+        <v>-6.098345948484249</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4958350789910972</v>
+        <v>0.516051245087958</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.554723821290553</v>
+        <v>-1.504183406048397</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.022911756021073</v>
+        <v>2.053236005166367</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712288</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.908455866921541</v>
+        <v>-5.857915451679389</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.593750354337919</v>
+        <v>0.6139665204347793</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.314293324485693</v>
+        <v>-1.263752909243537</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.168913130728867</v>
+        <v>2.199237379874161</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.665665059272095</v>
+        <v>-5.615124644029944</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.694795991232517</v>
+        <v>0.7150121573293777</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.314293324485693</v>
+        <v>-1.263752909243537</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.172842444563687</v>
+        <v>2.203166693708981</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.54972520964691</v>
+        <v>-5.499184794404758</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7418505149999315</v>
+        <v>0.7620666810967918</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.237471593469569</v>
+        <v>-1.186931178227413</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.219614067090702</v>
+        <v>2.249938316235995</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.307069621223746</v>
+        <v>-5.256529205981595</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8359108215891902</v>
+        <v>0.8561269876860509</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.237471593469569</v>
+        <v>-1.186931178227413</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.216612138310695</v>
+        <v>2.246936387455989</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145934</v>
+        <v>3.818665376145932</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.087048823186736</v>
+        <v>-5.036508407944584</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9254981778146085</v>
+        <v>0.9457143439114692</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.096251748401589</v>
+        <v>-1.045711333159433</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.302923082362097</v>
+        <v>2.333247331507391</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009946</v>
+        <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.887800193281927</v>
+        <v>-4.837259778039775</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.021091812578355</v>
+        <v>1.041307978675216</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.096251748401589</v>
+        <v>-1.045711333159433</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.318817265163921</v>
+        <v>2.349141514309214</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966254</v>
+        <v>3.845043810966252</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.728285089762557</v>
+        <v>-4.677744674520405</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.086043698426405</v>
+        <v>1.106259864523266</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.9367366448822186</v>
+        <v>-0.8861962296400626</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.415672171715844</v>
+        <v>2.445996420861138</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046989</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.58361294466282</v>
+        <v>-4.533072529420668</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.15400065902774</v>
+        <v>1.174216825124601</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7920644997824813</v>
+        <v>-0.7415240845403253</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.512563561337127</v>
+        <v>2.54288781048242</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412098</v>
+        <v>3.735835647412096</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.694533210670747</v>
+        <v>-4.515303070489712</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.024972244711291</v>
+        <v>1.096664300783705</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.9029847657904089</v>
+        <v>-0.7237546256093697</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.361351093819092</v>
+        <v>2.468889177927716</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144511</v>
+        <v>3.762643902144509</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.607733712891738</v>
+        <v>-4.428503572710703</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.08209253714546</v>
+        <v>1.153784593217875</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.9029847657904089</v>
+        <v>-0.7237546256093697</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.383751587141658</v>
+        <v>2.491289671250282</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900689</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.508041098162726</v>
+        <v>-4.328810957981691</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.122041984410477</v>
+        <v>1.193734040482891</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.8032921510613971</v>
+        <v>-0.6240620108803578</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.443639557352477</v>
+        <v>2.551177641461101</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473594</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.576411284486737</v>
+        <v>-4.397181144305701</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.105700832355575</v>
+        <v>1.177392888427989</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.7940164520251821</v>
+        <v>-0.6147863118441429</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.460211899248908</v>
+        <v>2.567749983357532</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978363</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.45499485486026</v>
+        <v>-4.275764714679225</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.144704112838057</v>
+        <v>1.216396168910471</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.7940164520251821</v>
+        <v>-0.6147863118441429</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.4506486078808</v>
+        <v>2.558186691989423</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887698</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.485988014188965</v>
+        <v>-4.30675787400793</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9570164141469619</v>
+        <v>1.028708470219376</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.7940164520251821</v>
+        <v>-0.6147863118441429</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.275358172921186</v>
+        <v>2.38289625702981</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675896</v>
+        <v>3.746038950675894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.310513754396496</v>
+        <v>-4.131283614215461</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.031773350055738</v>
+        <v>1.103465406128151</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.7940164520251821</v>
+        <v>-0.6147863118441429</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.279925404912974</v>
+        <v>2.387463489021598</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695441</v>
+        <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.421450007037745</v>
+        <v>-4.242219866856709</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9874103228860354</v>
+        <v>1.059102378958449</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.7940164520251821</v>
+        <v>-0.6147863118441429</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.279936878799772</v>
+        <v>2.387474962908395</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581285</v>
       </c>
       <c r="C1941" t="n">
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.624476584580978</v>
+        <v>-4.445246444399943</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9093310770886478</v>
+        <v>0.9810231331610617</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.9970430295684155</v>
+        <v>-0.8178128893873763</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.161252317493737</v>
+        <v>2.268790401602361</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734157</v>
+        <v>3.784340376734154</v>
       </c>
       <c r="C1942" t="n">
         <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.466550985645685</v>
+        <v>-4.28732084546465</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9826737030948973</v>
+        <v>1.054365759167311</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.9970430295684155</v>
+        <v>-0.8178128893873763</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.17142470392587</v>
+        <v>2.278962788034493</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.56479303264555</v>
+        <v>3.486590590890816</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.58920188715285</v>
+        <v>2.764596792240779</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.35651960863218</v>
+        <v>-4.186027142824996</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8462376193862307</v>
+        <v>1.089829510797033</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.9970430295684155</v>
+        <v>-0.8178128893873763</v>
       </c>
       <c r="G1943" t="n">
-        <v>1.990976069411801</v>
+        <v>2.273909058608353</v>
       </c>
     </row>
   </sheetData>
